--- a/notebooks/rda-experiments/runs/v10-sample3/evaluation_results.xlsx
+++ b/notebooks/rda-experiments/runs/v10-sample3/evaluation_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="169">
   <si>
     <t>fields in reference</t>
   </si>
@@ -155,40 +155,196 @@
     <t>dmp.dataset[2].type</t>
   </si>
   <si>
+    <t>dmp.dmp_id.identifier</t>
+  </si>
+  <si>
+    <t>dmp.dmp_id.type</t>
+  </si>
+  <si>
+    <t>dmp.ethical_issues_exist</t>
+  </si>
+  <si>
+    <t>dmp.language</t>
+  </si>
+  <si>
+    <t>dmp.modified</t>
+  </si>
+  <si>
+    <t>dmp.title</t>
+  </si>
+  <si>
+    <t>dmp.dataset[0].description</t>
+  </si>
+  <si>
+    <t>dmp.dataset[0].distribution[0].host.title</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].description</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].metadata[0].description</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].metadata[0].language</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].metadata[1].description</t>
+  </si>
+  <si>
+    <t>dmp.dataset[2].description</t>
+  </si>
+  <si>
+    <t>dmp.dataset[2].distribution[0].license[0].license_ref</t>
+  </si>
+  <si>
+    <t>dmp.dataset[2].metadata[0].language</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].description</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].metadata[0].language</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].personal_data</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].sensitive_data</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].title</t>
+  </si>
+  <si>
+    <t>dmp.description</t>
+  </si>
+  <si>
+    <t>0000-0003-0644-4174</t>
+  </si>
+  <si>
+    <t>orcid</t>
+  </si>
+  <si>
+    <t>2026-10-19T00:00:00Z</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Data related to each of our proposed experiments</t>
+  </si>
+  <si>
+    <t>dataset</t>
+  </si>
+  <si>
+    <t>Code and results for all analyses completed on experimental data</t>
+  </si>
+  <si>
+    <t>Simulation code for controller development and testing</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>CPS 2015</t>
+  </si>
+  <si>
+    <t>data related to each of our proposed experiments</t>
+  </si>
+  <si>
+    <t>code and results for all analyses completed on experimental data</t>
+  </si>
+  <si>
+    <t>simulation code for controller development and testing</t>
+  </si>
+  <si>
+    <t>First, we will have data related to each of our proposed experiments. These will include the detailed protocols used for each experiment, the raw data collected from each experiment, and the experimental code used to collect those data. The relevant code will include both the data acquisition code, and the code for the controllers used in the experiment. Together, this information will be sufficient for recreating the circumstances of each data collection session.</t>
+  </si>
+  <si>
+    <t>servers at the Rehabilitation Institute of Chicago</t>
+  </si>
+  <si>
+    <t>Our second type of data will be the code and results for all analyses completed on experimental data. Specifically, we store all code necessary to recreate figures, tables, and other results reported in all published manuscripts.</t>
+  </si>
+  <si>
+    <t>The contents of each data file, including the experimental conditions or the analysis procedures used during generation will be documented.</t>
+  </si>
+  <si>
+    <t>The code needed to generate all published results will be documented clearly.</t>
+  </si>
+  <si>
+    <t>The proposed foundational developments will produce substantial simulation code for controller development and testing. These and the outputs relevant to all key findings will also be managed.</t>
+  </si>
+  <si>
+    <t>GNU Public License</t>
+  </si>
+  <si>
+    <t>Select videos of the experiments will be distributed, with subject faces blurred so as to be unidentifiable.</t>
+  </si>
+  <si>
+    <t>videos of the experiments</t>
+  </si>
+  <si>
+    <t>We will manage all scientific and technical content generated from this proposal. Our products will include 3 broad types of data.</t>
+  </si>
+  <si>
+    <t>Hallucinated</t>
+  </si>
+  <si>
+    <t>Correct</t>
+  </si>
+  <si>
+    <t>Missed</t>
+  </si>
+  <si>
+    <t>not in the reference</t>
+  </si>
+  <si>
+    <t>both empty</t>
+  </si>
+  <si>
     <t>dmp.dataset[3].dataset_id.identifier</t>
   </si>
   <si>
     <t>dmp.dataset[3].dataset_id.type</t>
   </si>
   <si>
-    <t>dmp.dataset[3].personal_data</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].sensitive_data</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].title</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].type</t>
-  </si>
-  <si>
-    <t>dmp.dmp_id.identifier</t>
-  </si>
-  <si>
-    <t>dmp.dmp_id.type</t>
-  </si>
-  <si>
-    <t>dmp.ethical_issues_exist</t>
-  </si>
-  <si>
-    <t>dmp.language</t>
-  </si>
-  <si>
-    <t>dmp.modified</t>
-  </si>
-  <si>
-    <t>dmp.title</t>
+    <t>dmp.dataset[4].dataset_id.identifier</t>
+  </si>
+  <si>
+    <t>dmp.dataset[4].dataset_id.type</t>
+  </si>
+  <si>
+    <t>dmp.dataset[4].personal_data</t>
+  </si>
+  <si>
+    <t>dmp.dataset[4].sensitive_data</t>
+  </si>
+  <si>
+    <t>dmp.dataset[4].title</t>
+  </si>
+  <si>
+    <t>dmp.dataset[4].description</t>
+  </si>
+  <si>
+    <t>dmp.dataset[5].dataset_id.identifier</t>
+  </si>
+  <si>
+    <t>dmp.dataset[5].dataset_id.type</t>
+  </si>
+  <si>
+    <t>dmp.dataset[5].personal_data</t>
+  </si>
+  <si>
+    <t>dmp.dataset[5].sensitive_data</t>
+  </si>
+  <si>
+    <t>dmp.dataset[5].title</t>
+  </si>
+  <si>
+    <t>dmp.dataset[5].description</t>
   </si>
   <si>
     <t>dmp.project[0].title</t>
@@ -197,151 +353,43 @@
     <t>dmp.project[0].description</t>
   </si>
   <si>
-    <t>dmp.project[0].funding[0].funder_id.identifier</t>
-  </si>
-  <si>
-    <t>dmp.project[0].funding[0].funder_id.type</t>
-  </si>
-  <si>
-    <t>dmp.project[0].funding[0].funding_status</t>
-  </si>
-  <si>
-    <t>dmp.related_identifier[0].identifier</t>
-  </si>
-  <si>
-    <t>dmp.related_identifier[0].relation_type</t>
-  </si>
-  <si>
-    <t>dmp.related_identifier[0].type</t>
-  </si>
-  <si>
-    <t>dmp.dataset[0].description</t>
-  </si>
-  <si>
-    <t>dmp.dataset[0].distribution[0].host.title</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].description</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].metadata[0].description</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].metadata[0].language</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].metadata[1].description</t>
-  </si>
-  <si>
-    <t>dmp.dataset[2].description</t>
-  </si>
-  <si>
-    <t>dmp.dataset[2].distribution[0].license[0].license_ref</t>
-  </si>
-  <si>
-    <t>dmp.dataset[2].metadata[0].language</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].description</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].metadata[0].language</t>
-  </si>
-  <si>
-    <t>dmp.description</t>
-  </si>
-  <si>
     <t>other</t>
   </si>
   <si>
-    <t>2026-10-19T00:00:00Z</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>Data related to each of our proposed experiments</t>
-  </si>
-  <si>
-    <t>dataset</t>
-  </si>
-  <si>
-    <t>Code and results for all analyses completed on experimental data</t>
-  </si>
-  <si>
-    <t>Simulation code for controller development and testing</t>
-  </si>
-  <si>
-    <t>Software generated under the project</t>
-  </si>
-  <si>
-    <t>eng</t>
-  </si>
-  <si>
-    <t>CPS 2015</t>
-  </si>
-  <si>
-    <t>The project aims to manage and disseminate data generated by the project.</t>
-  </si>
-  <si>
-    <t>planned</t>
-  </si>
-  <si>
-    <t>isPartOf</t>
-  </si>
-  <si>
-    <t>data related to each of our proposed experiments</t>
-  </si>
-  <si>
-    <t>code and results for all analyses completed on experimental data</t>
-  </si>
-  <si>
-    <t>simulation code for controller development and testing</t>
-  </si>
-  <si>
-    <t>videos of the experiments</t>
-  </si>
-  <si>
-    <t>First, we will have data related to each of our proposed experiments. These will include the detailed protocols used for each experiment, the raw data collected from each experiment, and the experimental code used to collect those data. The relevant code will include both the data acquisition code, and the code for the controllers used in the experiment. Together, this information will be sufficient for recreating the circumstances of each data collection session.</t>
-  </si>
-  <si>
-    <t>servers at the Rehabilitation Institute of Chicago</t>
-  </si>
-  <si>
-    <t>Our second type of data will be the code and results for all analyses completed on experimental data. Specifically, we store all code necessary to recreate figures, tables, and other results reported in all published manuscripts.</t>
-  </si>
-  <si>
-    <t>The contents of each data file, including the experimental conditions or the analysis procedures used during generation will be documented.</t>
-  </si>
-  <si>
-    <t>The code needed to generate all published results will be documented clearly.</t>
-  </si>
-  <si>
-    <t>The proposed foundational developments will produce substantial simulation code for controller development and testing. These and the outputs relevant to all key findings will also be managed.</t>
-  </si>
-  <si>
-    <t>GNU Public License</t>
-  </si>
-  <si>
-    <t>Select videos of the experiments will be distributed, with subject faces blurred so as to be unidentifiable.</t>
-  </si>
-  <si>
-    <t>We will manage all scientific and technical content generated from this proposal. Our products will include 3 broad types of data.</t>
-  </si>
-  <si>
-    <t>Correct</t>
-  </si>
-  <si>
-    <t>Hallucinated</t>
-  </si>
-  <si>
-    <t>Missed</t>
-  </si>
-  <si>
-    <t>both empty</t>
-  </si>
-  <si>
-    <t>not in the reference</t>
+    <t>These will include the detailed protocols used for each experiment, the raw data collected from each experiment, and the experimental code used to collect those data. The relevant code will include both the data acquisition code, and the code for the controllers used in the experiment. Together, this information will be sufficient for recreating the circumstances of each data collection session.</t>
+  </si>
+  <si>
+    <t>We store all code necessary to recreate figures, tables, and other results reported in all published manuscripts. The proposed foundational developments will produce substantial simulation code for controller development and testing. These and the outputs relevant to all key findings will also be managed.</t>
+  </si>
+  <si>
+    <t>experimental analyses results</t>
+  </si>
+  <si>
+    <t>Experimental analyses results will be made available through peer-reviewed journal publications and conference presentations.</t>
+  </si>
+  <si>
+    <t>software generated under the project</t>
+  </si>
+  <si>
+    <t>Software generated under the project will be released under the GNU Public License, and available for free download on the labs’ websites. This includes code for each of our 3 experimental systems.</t>
+  </si>
+  <si>
+    <t>raw data files</t>
+  </si>
+  <si>
+    <t>Raw data files will be saved in either Matlab or comma-separated value (CSV) format. The contents of each data file, including the experimental conditions or the analysis procedures used during generation will be documented. All raw data will be de-identified to ensure subject anonynimity.</t>
+  </si>
+  <si>
+    <t>The Data Management Plan should clearly articulate how the PI and co-PIs plan to manage and disseminate data generated by the project. The plan should outline the rights and obligations of all parties as to their roles and responsibilities in the management and retention of research data, and consider changes that would occur should a PI or co-PI leave the institution or project. Any costs should be explained in the Budget Justification pages. Data will be generated at each of our institutional sites. The PI at each institution will be responsible for following the data management guidelines described below, and for saving the data to the RIC servers. This process of transferring all data to a central location will be facilitated by our research project coordinator. Our data management guidelines will be reviewed at the kickoff meeting for the project, and revisited briefly at each of our quarterly meetings with the PIs.</t>
+  </si>
+  <si>
+    <t>only 56% of the model's words are in the reference</t>
+  </si>
+  <si>
+    <t>different value</t>
+  </si>
+  <si>
+    <t>only 0% of the model's words are in the reference</t>
   </si>
   <si>
     <t>only 20% of the model's words are in the reference</t>
@@ -353,15 +401,12 @@
     <t>dmp.dataset[0].distribution[0].title</t>
   </si>
   <si>
+    <t>dmp.dataset[0].distribution[0].description</t>
+  </si>
+  <si>
     <t>dmp.dataset[0].distribution[0].host.url</t>
   </si>
   <si>
-    <t>dmp.dataset[0].distribution[0].license[0].license_ref</t>
-  </si>
-  <si>
-    <t>dmp.dataset[0].distribution[0].license[0].start_date</t>
-  </si>
-  <si>
     <t>dmp.dataset[0].metadata[0].language</t>
   </si>
   <si>
@@ -380,18 +425,15 @@
     <t>dmp.dataset[1].distribution[0].title</t>
   </si>
   <si>
+    <t>dmp.dataset[1].distribution[0].description</t>
+  </si>
+  <si>
     <t>dmp.dataset[1].distribution[0].host.title</t>
   </si>
   <si>
     <t>dmp.dataset[1].distribution[0].host.url</t>
   </si>
   <si>
-    <t>dmp.dataset[1].distribution[0].license[0].license_ref</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].distribution[0].license[0].start_date</t>
-  </si>
-  <si>
     <t>dmp.dataset[1].metadata[0].metadata_standard_id[0].identifier</t>
   </si>
   <si>
@@ -404,15 +446,15 @@
     <t>dmp.dataset[2].distribution[0].title</t>
   </si>
   <si>
+    <t>dmp.dataset[2].distribution[0].description</t>
+  </si>
+  <si>
     <t>dmp.dataset[2].distribution[0].host.title</t>
   </si>
   <si>
     <t>dmp.dataset[2].distribution[0].host.url</t>
   </si>
   <si>
-    <t>dmp.dataset[2].distribution[0].license[0].start_date</t>
-  </si>
-  <si>
     <t>dmp.dataset[2].metadata[0].metadata_standard_id[0].identifier</t>
   </si>
   <si>
@@ -422,58 +464,67 @@
     <t>dmp.dataset[2].metadata[0].description</t>
   </si>
   <si>
-    <t>These will include the detailed protocols used for each experiment, the raw data collected from each experiment, and the experimental code used to collect those data. The relevant code will include both the data acquisition code, and the code for the controllers used in the experiment. Together, this information will be sufficient for recreating the circumstances of each data collection session.</t>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Experimental data</t>
+  </si>
+  <si>
+    <t>Data related to each of our proposed experiments. These will include the detailed protocols used for each experiment, the raw data collected from each experiment, and the experimental code used to collect those data.</t>
   </si>
   <si>
     <t>shared</t>
   </si>
   <si>
-    <t>Rehabilitation Institute of Chicago</t>
-  </si>
-  <si>
-    <t>2026-10-19</t>
-  </si>
-  <si>
-    <t>Specifically, we store all code necessary to recreate figures, tables, and other results reported in all published manuscripts. The proposed foundational developments will produce substantial simulation code for controller development and testing. These and the outputs relevant to all key findings will also be managed.</t>
-  </si>
-  <si>
-    <t>These and the outputs relevant to all key findings will also be managed.</t>
-  </si>
-  <si>
-    <t>unknown</t>
+    <t>Experimental data distribution</t>
+  </si>
+  <si>
+    <t>Data will be made available upon request, after the conclusion of each of study.</t>
+  </si>
+  <si>
+    <t>Rehabilitation Institute of Chicago servers</t>
+  </si>
+  <si>
+    <t>Analysis code and results</t>
+  </si>
+  <si>
+    <t>Code and results for all analyses completed on experimental data.</t>
+  </si>
+  <si>
+    <t>Analysis code and results distribution</t>
+  </si>
+  <si>
+    <t>Code needed to generate all published results will be documented clearly.</t>
+  </si>
+  <si>
+    <t>Project website</t>
+  </si>
+  <si>
+    <t>Simulation code</t>
+  </si>
+  <si>
+    <t>Substantial simulation code for controller development and testing.</t>
+  </si>
+  <si>
+    <t>Simulation code distribution</t>
+  </si>
+  <si>
+    <t>Software generated under the project will be released under the GNU Public License.</t>
+  </si>
+  <si>
+    <t>CPS 2015 Data Management Plan</t>
   </si>
   <si>
     <t>null</t>
   </si>
   <si>
-    <t>only 57% of the model's words are in the reference</t>
+    <t>only 50% of the model's words are in the reference</t>
   </si>
   <si>
     <t>empty where the reference has a value</t>
   </si>
   <si>
-    <t>dmp.dataset[4].dataset_id.identifier</t>
-  </si>
-  <si>
-    <t>dmp.dataset[4].dataset_id.type</t>
-  </si>
-  <si>
-    <t>dmp.dataset[4].personal_data</t>
-  </si>
-  <si>
-    <t>dmp.dataset[4].sensitive_data</t>
-  </si>
-  <si>
-    <t>dmp.dataset[4].title</t>
-  </si>
-  <si>
-    <t>dmp.dataset[4].type</t>
-  </si>
-  <si>
-    <t>Data related to proposed experiments</t>
-  </si>
-  <si>
-    <t>Select videos of the experiments</t>
+    <t>only 40% of the model's words are in the reference</t>
   </si>
 </sst>
 </file>
@@ -880,34 +931,34 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0.512</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H2">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="I2">
-        <v>0.495</v>
+        <v>0.506</v>
       </c>
       <c r="J2">
-        <v>0.3928571428571428</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="K2">
-        <v>0.375</v>
+        <v>0.2045454545454546</v>
       </c>
       <c r="L2">
-        <v>0.2321428571428572</v>
+        <v>0.3409090909090909</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -918,34 +969,34 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>0.5570000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="H3">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="I3">
-        <v>0.596</v>
+        <v>0.464</v>
       </c>
       <c r="J3">
-        <v>0.4857142857142857</v>
+        <v>0.421875</v>
       </c>
       <c r="K3">
-        <v>0.3857142857142857</v>
+        <v>0.34375</v>
       </c>
       <c r="L3">
-        <v>0.1285714285714286</v>
+        <v>0.234375</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -956,34 +1007,34 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>0.537</v>
+        <v>0.536</v>
       </c>
       <c r="H4">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="I4">
-        <v>0.528</v>
+        <v>0.506</v>
       </c>
       <c r="J4">
-        <v>0.4150943396226415</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="K4">
-        <v>0.3584905660377358</v>
+        <v>0.3768115942028986</v>
       </c>
       <c r="L4">
-        <v>0.2264150943396226</v>
+        <v>0.1884057971014493</v>
       </c>
     </row>
   </sheetData>
@@ -993,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1029,11 +1080,14 @@
       <c r="C2" t="s">
         <v>22</v>
       </c>
+      <c r="D2" t="s">
+        <v>66</v>
+      </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1047,13 +1101,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1067,10 +1121,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1084,10 +1138,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G5" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1101,13 +1155,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G6" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1121,10 +1175,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G7" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1137,14 +1191,11 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
-        <v>77</v>
-      </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G8" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1158,13 +1209,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1178,13 +1229,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1198,13 +1249,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1218,13 +1269,13 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F12" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1238,10 +1289,10 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1254,14 +1305,11 @@
       <c r="C14" t="s">
         <v>34</v>
       </c>
-      <c r="D14" t="s">
-        <v>77</v>
-      </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1275,13 +1323,13 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1295,13 +1343,13 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1315,13 +1363,13 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="F17" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1335,13 +1383,13 @@
         <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F18" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1355,10 +1403,10 @@
         <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1371,14 +1419,11 @@
       <c r="C20" t="s">
         <v>40</v>
       </c>
-      <c r="D20" t="s">
-        <v>77</v>
-      </c>
       <c r="F20" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1392,13 +1437,13 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1412,13 +1457,13 @@
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1432,13 +1477,13 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1452,13 +1497,13 @@
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F24" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1472,10 +1517,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1488,14 +1533,11 @@
       <c r="C26" t="s">
         <v>46</v>
       </c>
-      <c r="D26" t="s">
-        <v>77</v>
-      </c>
       <c r="F26" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1509,13 +1551,13 @@
         <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
-      </c>
-      <c r="E27" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G27" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1529,13 +1571,13 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G28" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1549,16 +1591,13 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F29" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1572,13 +1611,13 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>76</v>
+      </c>
+      <c r="E30" t="s">
+        <v>76</v>
       </c>
       <c r="F30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G30" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1588,14 +1627,11 @@
       <c r="B31" t="s">
         <v>51</v>
       </c>
-      <c r="C31" t="s">
-        <v>51</v>
+      <c r="E31" t="s">
+        <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>103</v>
-      </c>
-      <c r="G31" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1605,254 +1641,182 @@
       <c r="B32" t="s">
         <v>52</v>
       </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" t="s">
-        <v>77</v>
+      <c r="E32" t="s">
+        <v>81</v>
       </c>
       <c r="F32" t="s">
-        <v>104</v>
-      </c>
-      <c r="G32" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>3</v>
       </c>
       <c r="B33" t="s">
         <v>53</v>
       </c>
-      <c r="C33" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" t="s">
-        <v>79</v>
+      <c r="E33" t="s">
+        <v>82</v>
       </c>
       <c r="F33" t="s">
-        <v>104</v>
-      </c>
-      <c r="G33" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>3</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
       </c>
-      <c r="C34" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" t="s">
-        <v>85</v>
+      <c r="E34" t="s">
+        <v>83</v>
       </c>
       <c r="F34" t="s">
-        <v>104</v>
-      </c>
-      <c r="G34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>3</v>
       </c>
       <c r="B35" t="s">
         <v>55</v>
       </c>
-      <c r="C35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" t="s">
-        <v>78</v>
+      <c r="E35" t="s">
+        <v>75</v>
       </c>
       <c r="F35" t="s">
-        <v>104</v>
-      </c>
-      <c r="G35" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>3</v>
       </c>
       <c r="B36" t="s">
         <v>56</v>
       </c>
-      <c r="C36" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36" t="s">
-        <v>86</v>
-      </c>
       <c r="E36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F36" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>3</v>
       </c>
       <c r="B37" t="s">
         <v>57</v>
       </c>
-      <c r="C37" t="s">
-        <v>57</v>
-      </c>
-      <c r="D37" t="s">
-        <v>86</v>
+      <c r="E37" t="s">
+        <v>85</v>
       </c>
       <c r="F37" t="s">
-        <v>104</v>
-      </c>
-      <c r="G37" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>3</v>
       </c>
       <c r="B38" t="s">
         <v>58</v>
       </c>
-      <c r="C38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" t="s">
-        <v>87</v>
+      <c r="E38" t="s">
+        <v>86</v>
       </c>
       <c r="F38" t="s">
-        <v>104</v>
-      </c>
-      <c r="G38" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>3</v>
       </c>
       <c r="B39" t="s">
         <v>59</v>
       </c>
-      <c r="C39" t="s">
-        <v>59</v>
+      <c r="E39" t="s">
+        <v>75</v>
       </c>
       <c r="F39" t="s">
-        <v>103</v>
-      </c>
-      <c r="G39" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>3</v>
       </c>
       <c r="B40" t="s">
         <v>60</v>
       </c>
-      <c r="C40" t="s">
-        <v>60</v>
-      </c>
-      <c r="D40" t="s">
-        <v>77</v>
+      <c r="E40" t="s">
+        <v>87</v>
       </c>
       <c r="F40" t="s">
-        <v>104</v>
-      </c>
-      <c r="G40" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>3</v>
       </c>
       <c r="B41" t="s">
         <v>61</v>
       </c>
-      <c r="C41" t="s">
-        <v>61</v>
-      </c>
-      <c r="D41" t="s">
-        <v>88</v>
+      <c r="E41" t="s">
+        <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>104</v>
-      </c>
-      <c r="G41" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>3</v>
       </c>
       <c r="B42" t="s">
         <v>62</v>
       </c>
-      <c r="C42" t="s">
-        <v>62</v>
+      <c r="E42" t="s">
+        <v>69</v>
       </c>
       <c r="F42" t="s">
-        <v>103</v>
-      </c>
-      <c r="G42" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>3</v>
       </c>
       <c r="B43" t="s">
         <v>63</v>
       </c>
-      <c r="C43" t="s">
-        <v>63</v>
-      </c>
-      <c r="D43" t="s">
-        <v>89</v>
+      <c r="E43" t="s">
+        <v>69</v>
       </c>
       <c r="F43" t="s">
-        <v>104</v>
-      </c>
-      <c r="G43" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>3</v>
       </c>
       <c r="B44" t="s">
         <v>64</v>
       </c>
-      <c r="C44" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" t="s">
-        <v>77</v>
+      <c r="E44" t="s">
+        <v>88</v>
       </c>
       <c r="F44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G44" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>3</v>
       </c>
@@ -1860,178 +1824,10 @@
         <v>65</v>
       </c>
       <c r="E45" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F45" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>3</v>
-      </c>
-      <c r="B46" t="s">
-        <v>66</v>
-      </c>
-      <c r="E46" t="s">
-        <v>95</v>
-      </c>
-      <c r="F46" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>3</v>
-      </c>
-      <c r="B47" t="s">
-        <v>67</v>
-      </c>
-      <c r="E47" t="s">
-        <v>96</v>
-      </c>
-      <c r="F47" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>3</v>
-      </c>
-      <c r="B48" t="s">
-        <v>68</v>
-      </c>
-      <c r="E48" t="s">
-        <v>97</v>
-      </c>
-      <c r="F48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>3</v>
-      </c>
-      <c r="B49" t="s">
-        <v>69</v>
-      </c>
-      <c r="E49" t="s">
-        <v>85</v>
-      </c>
-      <c r="F49" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>3</v>
-      </c>
-      <c r="B50" t="s">
-        <v>70</v>
-      </c>
-      <c r="E50" t="s">
-        <v>98</v>
-      </c>
-      <c r="F50" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>3</v>
-      </c>
-      <c r="B51" t="s">
-        <v>71</v>
-      </c>
-      <c r="E51" t="s">
-        <v>99</v>
-      </c>
-      <c r="F51" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>3</v>
-      </c>
-      <c r="B52" t="s">
-        <v>72</v>
-      </c>
-      <c r="E52" t="s">
-        <v>100</v>
-      </c>
-      <c r="F52" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>3</v>
-      </c>
-      <c r="B53" t="s">
-        <v>73</v>
-      </c>
-      <c r="E53" t="s">
-        <v>85</v>
-      </c>
-      <c r="F53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>3</v>
-      </c>
-      <c r="B54" t="s">
-        <v>74</v>
-      </c>
-      <c r="E54" t="s">
-        <v>101</v>
-      </c>
-      <c r="F54" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>3</v>
-      </c>
-      <c r="B55" t="s">
-        <v>75</v>
-      </c>
-      <c r="E55" t="s">
-        <v>85</v>
-      </c>
-      <c r="F55" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>3</v>
-      </c>
-      <c r="B56" t="s">
-        <v>49</v>
-      </c>
-      <c r="E56" t="s">
-        <v>93</v>
-      </c>
-      <c r="F56" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>3</v>
-      </c>
-      <c r="B57" t="s">
-        <v>76</v>
-      </c>
-      <c r="E57" t="s">
-        <v>102</v>
-      </c>
-      <c r="F57" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2041,7 +1837,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2078,10 +1874,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2095,13 +1891,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2115,10 +1911,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2132,10 +1928,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G5" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2149,13 +1945,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G6" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2169,10 +1965,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G7" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2185,14 +1981,11 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
-        <v>77</v>
-      </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G8" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2206,13 +1999,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2226,13 +2019,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2246,13 +2039,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2260,19 +2053,19 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2280,19 +2073,16 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2300,16 +2090,16 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2317,19 +2107,19 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2337,16 +2127,19 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
-      </c>
-      <c r="G16" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2354,19 +2147,19 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>78</v>
+      </c>
+      <c r="E17" t="s">
+        <v>78</v>
       </c>
       <c r="F17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G17" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2374,19 +2167,22 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
         <v>113</v>
       </c>
-      <c r="C18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" t="s">
-        <v>137</v>
+      <c r="E18" t="s">
+        <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2394,19 +2190,16 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2414,16 +2207,16 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2431,19 +2224,22 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E21" t="s">
+        <v>69</v>
       </c>
       <c r="F21" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2451,19 +2247,22 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>69</v>
       </c>
       <c r="F22" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2471,16 +2270,19 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" t="s">
+        <v>88</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2488,19 +2290,19 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>87</v>
+      </c>
+      <c r="E24" t="s">
+        <v>87</v>
       </c>
       <c r="F24" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2508,19 +2310,16 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" t="s">
-        <v>79</v>
-      </c>
-      <c r="E25" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F25" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="G25" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2528,19 +2327,16 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="G26" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2548,19 +2344,22 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G27" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2568,22 +2367,22 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="F28" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2591,19 +2390,22 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>114</v>
+      </c>
+      <c r="E29" t="s">
+        <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2611,16 +2413,22 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>60</v>
+      </c>
+      <c r="D30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" t="s">
+        <v>85</v>
       </c>
       <c r="F30" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2628,22 +2436,16 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" t="s">
-        <v>136</v>
-      </c>
-      <c r="E31" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="F31" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G31" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2651,16 +2453,16 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="F32" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G32" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2668,19 +2470,19 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2688,19 +2490,19 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="D34" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="F34" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2708,19 +2510,19 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s">
-        <v>85</v>
-      </c>
-      <c r="E35" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="F35" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G35" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2728,16 +2530,19 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>102</v>
+      </c>
+      <c r="D36" t="s">
+        <v>117</v>
       </c>
       <c r="F36" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2745,19 +2550,16 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
-      </c>
-      <c r="D37" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="F37" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G37" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2765,19 +2567,16 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E38" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F38" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2785,16 +2584,19 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>105</v>
+      </c>
+      <c r="D39" t="s">
+        <v>74</v>
       </c>
       <c r="F39" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G39" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2802,19 +2604,19 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F40" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G40" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2822,19 +2624,19 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
-      </c>
-      <c r="E41" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="F41" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G41" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2842,19 +2644,19 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
-      </c>
-      <c r="E42" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="F42" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G42" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2862,19 +2664,16 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" t="s">
-        <v>92</v>
-      </c>
-      <c r="E43" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="F43" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="G43" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2882,19 +2681,16 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C44" t="s">
-        <v>71</v>
-      </c>
-      <c r="D44" t="s">
-        <v>139</v>
-      </c>
-      <c r="E44" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="G44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2902,19 +2698,19 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="C45" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="F45" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2922,16 +2718,19 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="C46" t="s">
-        <v>127</v>
+        <v>48</v>
+      </c>
+      <c r="D46" t="s">
+        <v>75</v>
       </c>
       <c r="F46" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2939,22 +2738,19 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>136</v>
-      </c>
-      <c r="E47" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="F47" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2962,16 +2758,19 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
-        <v>129</v>
+        <v>50</v>
+      </c>
+      <c r="D48" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" t="s">
+        <v>76</v>
       </c>
       <c r="F48" t="s">
-        <v>103</v>
-      </c>
-      <c r="G48" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2979,19 +2778,19 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
-      </c>
-      <c r="E49" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F49" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G49" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2999,19 +2798,19 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D50" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="F50" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3019,19 +2818,13 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" t="s">
-        <v>73</v>
-      </c>
-      <c r="D51" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F51" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3039,16 +2832,13 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>131</v>
-      </c>
-      <c r="C52" t="s">
-        <v>131</v>
+        <v>53</v>
+      </c>
+      <c r="E52" t="s">
+        <v>82</v>
       </c>
       <c r="F52" t="s">
-        <v>103</v>
-      </c>
-      <c r="G52" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3056,19 +2846,13 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>132</v>
-      </c>
-      <c r="C53" t="s">
-        <v>132</v>
-      </c>
-      <c r="D53" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="E53" t="s">
+        <v>83</v>
       </c>
       <c r="F53" t="s">
-        <v>104</v>
-      </c>
-      <c r="G53" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3076,16 +2860,13 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
-      </c>
-      <c r="C54" t="s">
-        <v>133</v>
+        <v>55</v>
+      </c>
+      <c r="E54" t="s">
+        <v>75</v>
       </c>
       <c r="F54" t="s">
-        <v>103</v>
-      </c>
-      <c r="G54" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3093,16 +2874,13 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
-      </c>
-      <c r="C55" t="s">
-        <v>51</v>
+        <v>56</v>
+      </c>
+      <c r="E55" t="s">
+        <v>84</v>
       </c>
       <c r="F55" t="s">
-        <v>103</v>
-      </c>
-      <c r="G55" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3110,19 +2888,13 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>52</v>
-      </c>
-      <c r="C56" t="s">
-        <v>52</v>
-      </c>
-      <c r="D56" t="s">
-        <v>77</v>
+        <v>57</v>
+      </c>
+      <c r="E56" t="s">
+        <v>85</v>
       </c>
       <c r="F56" t="s">
-        <v>104</v>
-      </c>
-      <c r="G56" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3130,19 +2902,13 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
-      </c>
-      <c r="C57" t="s">
-        <v>53</v>
-      </c>
-      <c r="D57" t="s">
-        <v>140</v>
+        <v>58</v>
+      </c>
+      <c r="E57" t="s">
+        <v>86</v>
       </c>
       <c r="F57" t="s">
-        <v>104</v>
-      </c>
-      <c r="G57" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3150,19 +2916,13 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
-      </c>
-      <c r="C58" t="s">
-        <v>54</v>
-      </c>
-      <c r="D58" t="s">
-        <v>85</v>
+        <v>59</v>
+      </c>
+      <c r="E58" t="s">
+        <v>75</v>
       </c>
       <c r="F58" t="s">
-        <v>104</v>
-      </c>
-      <c r="G58" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3170,19 +2930,13 @@
         <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
-      </c>
-      <c r="C59" t="s">
-        <v>55</v>
-      </c>
-      <c r="D59" t="s">
-        <v>78</v>
+        <v>41</v>
+      </c>
+      <c r="E59" t="s">
+        <v>69</v>
       </c>
       <c r="F59" t="s">
-        <v>104</v>
-      </c>
-      <c r="G59" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3190,19 +2944,13 @@
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C60" t="s">
-        <v>56</v>
-      </c>
-      <c r="D60" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E60" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="F60" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3210,16 +2958,13 @@
         <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
-      </c>
-      <c r="C61" t="s">
-        <v>57</v>
+        <v>43</v>
+      </c>
+      <c r="E61" t="s">
+        <v>79</v>
       </c>
       <c r="F61" t="s">
-        <v>103</v>
-      </c>
-      <c r="G61" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3227,19 +2972,13 @@
         <v>3</v>
       </c>
       <c r="B62" t="s">
-        <v>58</v>
-      </c>
-      <c r="C62" t="s">
-        <v>58</v>
-      </c>
-      <c r="D62" t="s">
-        <v>102</v>
+        <v>61</v>
+      </c>
+      <c r="E62" t="s">
+        <v>75</v>
       </c>
       <c r="F62" t="s">
-        <v>104</v>
-      </c>
-      <c r="G62" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3247,13 +2986,13 @@
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E63" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="F63" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3261,13 +3000,13 @@
         <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E64" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="F64" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3275,97 +3014,13 @@
         <v>3</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E65" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F65" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>3</v>
-      </c>
-      <c r="B66" t="s">
-        <v>74</v>
-      </c>
-      <c r="E66" t="s">
-        <v>101</v>
-      </c>
-      <c r="F66" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>3</v>
-      </c>
-      <c r="B67" t="s">
-        <v>75</v>
-      </c>
-      <c r="E67" t="s">
-        <v>85</v>
-      </c>
-      <c r="F67" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>3</v>
-      </c>
-      <c r="B68" t="s">
-        <v>47</v>
-      </c>
-      <c r="E68" t="s">
-        <v>79</v>
-      </c>
-      <c r="F68" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>3</v>
-      </c>
-      <c r="B69" t="s">
-        <v>48</v>
-      </c>
-      <c r="E69" t="s">
-        <v>79</v>
-      </c>
-      <c r="F69" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>3</v>
-      </c>
-      <c r="B70" t="s">
-        <v>49</v>
-      </c>
-      <c r="E70" t="s">
-        <v>93</v>
-      </c>
-      <c r="F70" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>3</v>
-      </c>
-      <c r="B71" t="s">
-        <v>76</v>
-      </c>
-      <c r="E71" t="s">
-        <v>102</v>
-      </c>
-      <c r="F71" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -3375,7 +3030,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3412,10 +3067,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3429,13 +3084,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3449,10 +3104,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3466,10 +3121,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G5" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3483,13 +3138,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G6" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3503,10 +3158,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G7" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3519,14 +3174,11 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
-        <v>77</v>
-      </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G8" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3540,13 +3192,16 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G9" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3560,13 +3215,16 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3580,13 +3238,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G11" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3594,19 +3255,19 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>150</v>
+      </c>
+      <c r="E12" t="s">
+        <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3614,16 +3275,19 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>125</v>
+      </c>
+      <c r="D13" t="s">
+        <v>151</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3631,19 +3295,19 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3651,19 +3315,19 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" t="s">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G15" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3671,19 +3335,19 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3691,19 +3355,16 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="F17" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="G17" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3711,19 +3372,19 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3731,16 +3392,16 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3748,19 +3409,19 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F20" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3768,19 +3429,19 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F21" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G21" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3788,19 +3449,16 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="G22" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3808,19 +3466,16 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="G23" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3828,19 +3483,19 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>69</v>
+      </c>
+      <c r="E24" t="s">
+        <v>69</v>
       </c>
       <c r="F24" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3848,16 +3503,19 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>36</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" t="s">
+        <v>69</v>
       </c>
       <c r="F25" t="s">
-        <v>103</v>
-      </c>
-      <c r="G25" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3865,19 +3523,19 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>77</v>
+        <v>155</v>
+      </c>
+      <c r="E26" t="s">
+        <v>78</v>
       </c>
       <c r="F26" t="s">
-        <v>104</v>
-      </c>
-      <c r="G26" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3885,19 +3543,19 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="E27" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3905,19 +3563,19 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G28" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3925,19 +3583,19 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="G29" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3945,19 +3603,19 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="F30" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3965,16 +3623,22 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
-        <v>144</v>
+        <v>136</v>
+      </c>
+      <c r="D31" t="s">
+        <v>159</v>
+      </c>
+      <c r="E31" t="s">
+        <v>165</v>
       </c>
       <c r="F31" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3982,19 +3646,16 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
-      </c>
-      <c r="D32" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="F32" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G32" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -4002,19 +3663,19 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>75</v>
+      </c>
+      <c r="E33" t="s">
+        <v>75</v>
       </c>
       <c r="F33" t="s">
-        <v>104</v>
-      </c>
-      <c r="G33" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -4022,19 +3683,16 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>147</v>
-      </c>
-      <c r="D34" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="F34" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G34" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -4042,19 +3700,19 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="F35" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -4062,19 +3720,19 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>149</v>
-      </c>
-      <c r="D36" t="s">
-        <v>81</v>
+        <v>54</v>
+      </c>
+      <c r="E36" t="s">
+        <v>83</v>
       </c>
       <c r="F36" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -4082,16 +3740,16 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F37" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G37" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4099,19 +3757,16 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="F38" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -4119,19 +3774,19 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>69</v>
+      </c>
+      <c r="E39" t="s">
+        <v>69</v>
       </c>
       <c r="F39" t="s">
-        <v>104</v>
-      </c>
-      <c r="G39" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -4139,19 +3794,19 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>85</v>
+        <v>69</v>
+      </c>
+      <c r="E40" t="s">
+        <v>69</v>
       </c>
       <c r="F40" t="s">
-        <v>104</v>
-      </c>
-      <c r="G40" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -4159,19 +3814,19 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>160</v>
+      </c>
+      <c r="E41" t="s">
+        <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>104</v>
-      </c>
-      <c r="G41" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4179,19 +3834,19 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D42" t="s">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="E42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F42" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -4199,13 +3854,19 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
-      </c>
-      <c r="E43" t="s">
-        <v>94</v>
+        <v>140</v>
+      </c>
+      <c r="C43" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" t="s">
+        <v>151</v>
       </c>
       <c r="F43" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="G43" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4213,13 +3874,19 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" t="s">
-        <v>95</v>
+        <v>141</v>
+      </c>
+      <c r="C44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D44" t="s">
+        <v>162</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="G44" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4227,13 +3894,19 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
-      </c>
-      <c r="E45" t="s">
-        <v>96</v>
+        <v>142</v>
+      </c>
+      <c r="C45" t="s">
+        <v>142</v>
+      </c>
+      <c r="D45" t="s">
+        <v>163</v>
       </c>
       <c r="F45" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="G45" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -4241,13 +3914,22 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>143</v>
+      </c>
+      <c r="C46" t="s">
+        <v>143</v>
+      </c>
+      <c r="D46" t="s">
+        <v>159</v>
       </c>
       <c r="E46" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="F46" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="G46" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -4255,13 +3937,16 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" t="s">
-        <v>85</v>
+        <v>144</v>
+      </c>
+      <c r="C47" t="s">
+        <v>144</v>
       </c>
       <c r="F47" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="G47" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -4269,97 +3954,372 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="C48" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48" t="s">
+        <v>75</v>
       </c>
       <c r="E48" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
-      </c>
-      <c r="E49" t="s">
-        <v>99</v>
+        <v>145</v>
+      </c>
+      <c r="C49" t="s">
+        <v>145</v>
       </c>
       <c r="F49" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>91</v>
+      </c>
+      <c r="G49" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
-      </c>
-      <c r="E50" t="s">
-        <v>100</v>
+        <v>146</v>
+      </c>
+      <c r="C50" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" t="s">
+        <v>111</v>
       </c>
       <c r="F50" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>90</v>
+      </c>
+      <c r="G50" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
-      </c>
-      <c r="E51" t="s">
-        <v>85</v>
+        <v>147</v>
+      </c>
+      <c r="C51" t="s">
+        <v>147</v>
       </c>
       <c r="F51" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>91</v>
+      </c>
+      <c r="G51" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
-      </c>
-      <c r="E52" t="s">
-        <v>101</v>
+        <v>45</v>
+      </c>
+      <c r="C52" t="s">
+        <v>45</v>
       </c>
       <c r="F52" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>91</v>
+      </c>
+      <c r="G52" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>3</v>
       </c>
       <c r="B53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F53" t="s">
+        <v>91</v>
+      </c>
+      <c r="G53" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" t="s">
+        <v>47</v>
+      </c>
+      <c r="D54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F54" t="s">
+        <v>90</v>
+      </c>
+      <c r="G54" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>3</v>
+      </c>
+      <c r="B55" t="s">
+        <v>48</v>
+      </c>
+      <c r="C55" t="s">
+        <v>48</v>
+      </c>
+      <c r="D55" t="s">
         <v>75</v>
       </c>
-      <c r="E53" t="s">
-        <v>85</v>
-      </c>
-      <c r="F53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>3</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="F55" t="s">
+        <v>90</v>
+      </c>
+      <c r="G55" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s">
+        <v>49</v>
+      </c>
+      <c r="C56" t="s">
+        <v>49</v>
+      </c>
+      <c r="D56" t="s">
+        <v>68</v>
+      </c>
+      <c r="F56" t="s">
+        <v>90</v>
+      </c>
+      <c r="G56" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s">
+        <v>50</v>
+      </c>
+      <c r="C57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D57" t="s">
+        <v>164</v>
+      </c>
+      <c r="E57" t="s">
         <v>76</v>
       </c>
-      <c r="E54" t="s">
-        <v>102</v>
-      </c>
-      <c r="F54" t="s">
-        <v>105</v>
+      <c r="F57" t="s">
+        <v>90</v>
+      </c>
+      <c r="G57" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" t="s">
+        <v>69</v>
+      </c>
+      <c r="F58" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>3</v>
+      </c>
+      <c r="B59" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" t="s">
+        <v>69</v>
+      </c>
+      <c r="F59" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" t="s">
+        <v>77</v>
+      </c>
+      <c r="F60" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>3</v>
+      </c>
+      <c r="B61" t="s">
+        <v>54</v>
+      </c>
+      <c r="E61" t="s">
+        <v>83</v>
+      </c>
+      <c r="F61" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>56</v>
+      </c>
+      <c r="E62" t="s">
+        <v>84</v>
+      </c>
+      <c r="F62" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" t="s">
+        <v>86</v>
+      </c>
+      <c r="F63" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s">
+        <v>60</v>
+      </c>
+      <c r="E64" t="s">
+        <v>87</v>
+      </c>
+      <c r="F64" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>61</v>
+      </c>
+      <c r="E65" t="s">
+        <v>75</v>
+      </c>
+      <c r="F65" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>62</v>
+      </c>
+      <c r="E66" t="s">
+        <v>69</v>
+      </c>
+      <c r="F66" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>63</v>
+      </c>
+      <c r="E67" t="s">
+        <v>69</v>
+      </c>
+      <c r="F67" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>3</v>
+      </c>
+      <c r="B68" t="s">
+        <v>64</v>
+      </c>
+      <c r="E68" t="s">
+        <v>88</v>
+      </c>
+      <c r="F68" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>3</v>
+      </c>
+      <c r="B69" t="s">
+        <v>65</v>
+      </c>
+      <c r="E69" t="s">
+        <v>89</v>
+      </c>
+      <c r="F69" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>3</v>
+      </c>
+      <c r="B70" t="s">
+        <v>50</v>
+      </c>
+      <c r="E70" t="s">
+        <v>76</v>
+      </c>
+      <c r="F70" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -4369,7 +4329,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -4411,11 +4371,14 @@
       <c r="D2" t="s">
         <v>22</v>
       </c>
+      <c r="E2" t="s">
+        <v>66</v>
+      </c>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4432,13 +4395,13 @@
         <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="G3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4455,10 +4418,10 @@
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4475,10 +4438,10 @@
         <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4495,13 +4458,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4518,10 +4481,10 @@
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4537,14 +4500,11 @@
       <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="E8" t="s">
-        <v>77</v>
-      </c>
       <c r="G8" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4561,13 +4521,13 @@
         <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4584,13 +4544,13 @@
         <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4607,13 +4567,13 @@
         <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4630,13 +4590,13 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G12" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -4653,10 +4613,10 @@
         <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4672,14 +4632,11 @@
       <c r="D14" t="s">
         <v>34</v>
       </c>
-      <c r="E14" t="s">
-        <v>77</v>
-      </c>
       <c r="G14" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4696,13 +4653,13 @@
         <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4719,13 +4676,13 @@
         <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4742,13 +4699,13 @@
         <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -4765,13 +4722,13 @@
         <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G18" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -4788,10 +4745,10 @@
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -4807,14 +4764,11 @@
       <c r="D20" t="s">
         <v>40</v>
       </c>
-      <c r="E20" t="s">
-        <v>77</v>
-      </c>
       <c r="G20" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -4831,13 +4785,13 @@
         <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G21" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -4854,13 +4808,13 @@
         <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G22" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4877,13 +4831,13 @@
         <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -4900,13 +4854,13 @@
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G24" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4923,10 +4877,10 @@
         <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4942,14 +4896,11 @@
       <c r="D26" t="s">
         <v>46</v>
       </c>
-      <c r="E26" t="s">
-        <v>77</v>
-      </c>
       <c r="G26" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4966,13 +4917,13 @@
         <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>79</v>
-      </c>
-      <c r="F27" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H27" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4989,13 +4940,13 @@
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>79</v>
-      </c>
-      <c r="F28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H28" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -5012,16 +4963,13 @@
         <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5038,13 +4986,13 @@
         <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>81</v>
+        <v>76</v>
+      </c>
+      <c r="F30" t="s">
+        <v>76</v>
       </c>
       <c r="G30" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5057,14 +5005,11 @@
       <c r="C31" t="s">
         <v>51</v>
       </c>
-      <c r="D31" t="s">
-        <v>51</v>
+      <c r="F31" t="s">
+        <v>80</v>
       </c>
       <c r="G31" t="s">
-        <v>103</v>
-      </c>
-      <c r="H31" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5077,17 +5022,11 @@
       <c r="C32" t="s">
         <v>52</v>
       </c>
-      <c r="D32" t="s">
-        <v>52</v>
-      </c>
-      <c r="E32" t="s">
-        <v>77</v>
+      <c r="F32" t="s">
+        <v>81</v>
       </c>
       <c r="G32" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -5100,17 +5039,11 @@
       <c r="C33" t="s">
         <v>53</v>
       </c>
-      <c r="D33" t="s">
-        <v>53</v>
-      </c>
-      <c r="E33" t="s">
-        <v>79</v>
+      <c r="F33" t="s">
+        <v>82</v>
       </c>
       <c r="G33" t="s">
-        <v>104</v>
-      </c>
-      <c r="H33" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -5123,17 +5056,11 @@
       <c r="C34" t="s">
         <v>54</v>
       </c>
-      <c r="D34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E34" t="s">
-        <v>85</v>
+      <c r="F34" t="s">
+        <v>83</v>
       </c>
       <c r="G34" t="s">
-        <v>104</v>
-      </c>
-      <c r="H34" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -5146,17 +5073,11 @@
       <c r="C35" t="s">
         <v>55</v>
       </c>
-      <c r="D35" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" t="s">
-        <v>78</v>
+      <c r="F35" t="s">
+        <v>75</v>
       </c>
       <c r="G35" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -5169,17 +5090,11 @@
       <c r="C36" t="s">
         <v>56</v>
       </c>
-      <c r="D36" t="s">
-        <v>56</v>
-      </c>
-      <c r="E36" t="s">
-        <v>86</v>
-      </c>
       <c r="F36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -5192,17 +5107,11 @@
       <c r="C37" t="s">
         <v>57</v>
       </c>
-      <c r="D37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E37" t="s">
-        <v>86</v>
+      <c r="F37" t="s">
+        <v>85</v>
       </c>
       <c r="G37" t="s">
-        <v>104</v>
-      </c>
-      <c r="H37" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -5215,17 +5124,11 @@
       <c r="C38" t="s">
         <v>58</v>
       </c>
-      <c r="D38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" t="s">
-        <v>87</v>
+      <c r="F38" t="s">
+        <v>86</v>
       </c>
       <c r="G38" t="s">
-        <v>104</v>
-      </c>
-      <c r="H38" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -5238,14 +5141,11 @@
       <c r="C39" t="s">
         <v>59</v>
       </c>
-      <c r="D39" t="s">
-        <v>59</v>
+      <c r="F39" t="s">
+        <v>75</v>
       </c>
       <c r="G39" t="s">
-        <v>103</v>
-      </c>
-      <c r="H39" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -5258,17 +5158,11 @@
       <c r="C40" t="s">
         <v>60</v>
       </c>
-      <c r="D40" t="s">
-        <v>60</v>
-      </c>
-      <c r="E40" t="s">
-        <v>77</v>
+      <c r="F40" t="s">
+        <v>87</v>
       </c>
       <c r="G40" t="s">
-        <v>104</v>
-      </c>
-      <c r="H40" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -5281,17 +5175,11 @@
       <c r="C41" t="s">
         <v>61</v>
       </c>
-      <c r="D41" t="s">
-        <v>61</v>
-      </c>
-      <c r="E41" t="s">
-        <v>88</v>
+      <c r="F41" t="s">
+        <v>75</v>
       </c>
       <c r="G41" t="s">
-        <v>104</v>
-      </c>
-      <c r="H41" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -5304,14 +5192,11 @@
       <c r="C42" t="s">
         <v>62</v>
       </c>
-      <c r="D42" t="s">
-        <v>62</v>
+      <c r="F42" t="s">
+        <v>69</v>
       </c>
       <c r="G42" t="s">
-        <v>103</v>
-      </c>
-      <c r="H42" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -5324,17 +5209,11 @@
       <c r="C43" t="s">
         <v>63</v>
       </c>
-      <c r="D43" t="s">
-        <v>63</v>
-      </c>
-      <c r="E43" t="s">
-        <v>89</v>
+      <c r="F43" t="s">
+        <v>69</v>
       </c>
       <c r="G43" t="s">
-        <v>104</v>
-      </c>
-      <c r="H43" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -5347,17 +5226,11 @@
       <c r="C44" t="s">
         <v>64</v>
       </c>
-      <c r="D44" t="s">
-        <v>64</v>
-      </c>
-      <c r="E44" t="s">
-        <v>77</v>
+      <c r="F44" t="s">
+        <v>88</v>
       </c>
       <c r="G44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H44" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -5371,10 +5244,10 @@
         <v>65</v>
       </c>
       <c r="F45" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -5382,16 +5255,19 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
-      </c>
-      <c r="F46" t="s">
-        <v>95</v>
+        <v>22</v>
+      </c>
+      <c r="D46" t="s">
+        <v>22</v>
       </c>
       <c r="G46" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="H46" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -5399,16 +5275,22 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>67</v>
-      </c>
-      <c r="F47" t="s">
-        <v>96</v>
+        <v>23</v>
+      </c>
+      <c r="D47" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" t="s">
+        <v>111</v>
       </c>
       <c r="G47" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="H47" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -5416,16 +5298,19 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>68</v>
-      </c>
-      <c r="F48" t="s">
-        <v>97</v>
+        <v>24</v>
+      </c>
+      <c r="D48" t="s">
+        <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="H48" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -5433,16 +5318,19 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>69</v>
-      </c>
-      <c r="F49" t="s">
-        <v>85</v>
+        <v>25</v>
+      </c>
+      <c r="D49" t="s">
+        <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="H49" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -5450,16 +5338,22 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
-      </c>
-      <c r="F50" t="s">
-        <v>98</v>
+        <v>26</v>
+      </c>
+      <c r="D50" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" t="s">
+        <v>68</v>
       </c>
       <c r="G50" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="H50" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -5467,16 +5361,19 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>71</v>
-      </c>
-      <c r="F51" t="s">
-        <v>99</v>
+        <v>27</v>
+      </c>
+      <c r="D51" t="s">
+        <v>27</v>
       </c>
       <c r="G51" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="H51" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -5484,16 +5381,19 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
-      </c>
-      <c r="F52" t="s">
-        <v>100</v>
+        <v>28</v>
+      </c>
+      <c r="D52" t="s">
+        <v>28</v>
       </c>
       <c r="G52" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="H52" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -5501,16 +5401,22 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>73</v>
+        <v>29</v>
+      </c>
+      <c r="D53" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" t="s">
+        <v>69</v>
       </c>
       <c r="F53" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G53" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -5518,16 +5424,22 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>74</v>
+        <v>30</v>
+      </c>
+      <c r="D54" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" t="s">
+        <v>69</v>
       </c>
       <c r="F54" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="G54" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -5535,16 +5447,22 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>75</v>
+        <v>31</v>
+      </c>
+      <c r="D55" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" t="s">
+        <v>77</v>
       </c>
       <c r="F55" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -5552,16 +5470,22 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="D56" t="s">
+        <v>51</v>
+      </c>
+      <c r="E56" t="s">
+        <v>112</v>
       </c>
       <c r="F56" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -5569,16 +5493,19 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
-      </c>
-      <c r="F57" t="s">
-        <v>102</v>
+        <v>33</v>
+      </c>
+      <c r="D57" t="s">
+        <v>33</v>
       </c>
       <c r="G57" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="H57" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -5589,16 +5516,16 @@
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D58" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G58" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -5609,19 +5536,19 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D59" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E59" t="s">
-        <v>77</v>
+        <v>69</v>
+      </c>
+      <c r="F59" t="s">
+        <v>69</v>
       </c>
       <c r="G59" t="s">
-        <v>104</v>
-      </c>
-      <c r="H59" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -5632,16 +5559,19 @@
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>36</v>
+      </c>
+      <c r="E60" t="s">
+        <v>69</v>
+      </c>
+      <c r="F60" t="s">
+        <v>69</v>
       </c>
       <c r="G60" t="s">
-        <v>103</v>
-      </c>
-      <c r="H60" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -5652,16 +5582,19 @@
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D61" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="E61" t="s">
+        <v>78</v>
+      </c>
+      <c r="F61" t="s">
+        <v>78</v>
       </c>
       <c r="G61" t="s">
-        <v>103</v>
-      </c>
-      <c r="H61" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -5672,19 +5605,22 @@
         <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="E62" t="s">
-        <v>78</v>
+        <v>113</v>
+      </c>
+      <c r="F62" t="s">
+        <v>82</v>
       </c>
       <c r="G62" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -5695,16 +5631,16 @@
         <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="D63" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G63" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -5715,19 +5651,16 @@
         <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E64" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="G64" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -5738,19 +5671,22 @@
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D65" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E65" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F65" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G65" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H65" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -5761,19 +5697,22 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D66" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E66" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F66" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G66" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H66" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -5784,19 +5723,19 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D67" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E67" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F67" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G67" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -5807,19 +5746,19 @@
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D68" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E68" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="F68" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G68" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -5830,19 +5769,16 @@
         <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
-      </c>
-      <c r="E69" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="G69" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H69" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -5853,16 +5789,16 @@
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="D70" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="G70" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H70" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -5873,19 +5809,22 @@
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="D71" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E71" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="F71" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="G71" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H71" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -5896,16 +5835,22 @@
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="D72" t="s">
-        <v>111</v>
+        <v>63</v>
+      </c>
+      <c r="E72" t="s">
+        <v>74</v>
+      </c>
+      <c r="F72" t="s">
+        <v>69</v>
       </c>
       <c r="G72" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -5916,19 +5861,22 @@
         <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="D73" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="E73" t="s">
-        <v>100</v>
+        <v>114</v>
+      </c>
+      <c r="F73" t="s">
+        <v>79</v>
       </c>
       <c r="G73" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -5939,19 +5887,22 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="E74" t="s">
-        <v>137</v>
+        <v>115</v>
+      </c>
+      <c r="F74" t="s">
+        <v>85</v>
       </c>
       <c r="G74" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -5962,19 +5913,16 @@
         <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D75" t="s">
-        <v>114</v>
-      </c>
-      <c r="E75" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="G75" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H75" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -5985,16 +5933,16 @@
         <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D76" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="G76" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -6005,19 +5953,19 @@
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="D77" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E77" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G77" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H77" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -6028,19 +5976,19 @@
         <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D78" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="E78" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="G78" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -6051,16 +5999,19 @@
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D79" t="s">
-        <v>33</v>
+        <v>101</v>
+      </c>
+      <c r="E79" t="s">
+        <v>116</v>
       </c>
       <c r="G79" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -6071,19 +6022,19 @@
         <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D80" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="E80" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="G80" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -6094,19 +6045,16 @@
         <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="D81" t="s">
-        <v>35</v>
-      </c>
-      <c r="E81" t="s">
-        <v>79</v>
-      </c>
-      <c r="F81" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="G81" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="H81" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -6117,19 +6065,16 @@
         <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="D82" t="s">
-        <v>36</v>
-      </c>
-      <c r="E82" t="s">
-        <v>79</v>
-      </c>
-      <c r="F82" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="G82" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="H82" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -6140,19 +6085,19 @@
         <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="D83" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="E83" t="s">
-        <v>91</v>
-      </c>
-      <c r="F83" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="G83" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H83" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -6163,22 +6108,19 @@
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="D84" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="E84" t="s">
-        <v>138</v>
-      </c>
-      <c r="F84" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="G84" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H84" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -6189,19 +6131,19 @@
         <v>13</v>
       </c>
       <c r="C85" t="s">
+        <v>107</v>
+      </c>
+      <c r="D85" t="s">
+        <v>107</v>
+      </c>
+      <c r="E85" t="s">
         <v>118</v>
       </c>
-      <c r="D85" t="s">
-        <v>118</v>
-      </c>
-      <c r="E85" t="s">
-        <v>135</v>
-      </c>
       <c r="G85" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H85" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -6212,16 +6154,19 @@
         <v>13</v>
       </c>
       <c r="C86" t="s">
+        <v>108</v>
+      </c>
+      <c r="D86" t="s">
+        <v>108</v>
+      </c>
+      <c r="E86" t="s">
         <v>119</v>
       </c>
-      <c r="D86" t="s">
-        <v>119</v>
-      </c>
       <c r="G86" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H86" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -6232,22 +6177,16 @@
         <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="D87" t="s">
-        <v>120</v>
-      </c>
-      <c r="E87" t="s">
-        <v>136</v>
-      </c>
-      <c r="F87" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="G87" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H87" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -6258,16 +6197,16 @@
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="D88" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="G88" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -6278,19 +6217,19 @@
         <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="D89" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="E89" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G89" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H89" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -6301,19 +6240,19 @@
         <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="D90" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="E90" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="G90" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H90" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -6324,19 +6263,19 @@
         <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E91" t="s">
-        <v>85</v>
-      </c>
-      <c r="F91" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="G91" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H91" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -6347,16 +6286,19 @@
         <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="D92" t="s">
-        <v>124</v>
+        <v>50</v>
+      </c>
+      <c r="E92" t="s">
+        <v>76</v>
+      </c>
+      <c r="F92" t="s">
+        <v>76</v>
       </c>
       <c r="G92" t="s">
-        <v>103</v>
-      </c>
-      <c r="H92" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -6367,19 +6309,19 @@
         <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D93" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="E93" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G93" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H93" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -6390,19 +6332,19 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="D94" t="s">
-        <v>68</v>
-      </c>
-      <c r="F94" t="s">
-        <v>97</v>
+        <v>110</v>
+      </c>
+      <c r="E94" t="s">
+        <v>120</v>
       </c>
       <c r="G94" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H94" t="s">
-        <v>143</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -6413,16 +6355,13 @@
         <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>39</v>
-      </c>
-      <c r="D95" t="s">
-        <v>39</v>
+        <v>52</v>
+      </c>
+      <c r="F95" t="s">
+        <v>81</v>
       </c>
       <c r="G95" t="s">
-        <v>103</v>
-      </c>
-      <c r="H95" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -6433,19 +6372,13 @@
         <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>40</v>
-      </c>
-      <c r="D96" t="s">
-        <v>40</v>
-      </c>
-      <c r="E96" t="s">
-        <v>77</v>
+        <v>53</v>
+      </c>
+      <c r="F96" t="s">
+        <v>82</v>
       </c>
       <c r="G96" t="s">
-        <v>104</v>
-      </c>
-      <c r="H96" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -6456,19 +6389,13 @@
         <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>41</v>
-      </c>
-      <c r="D97" t="s">
-        <v>41</v>
-      </c>
-      <c r="E97" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="F97" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G97" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -6479,19 +6406,13 @@
         <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>42</v>
-      </c>
-      <c r="D98" t="s">
-        <v>42</v>
-      </c>
-      <c r="E98" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F98" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G98" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -6502,19 +6423,13 @@
         <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>43</v>
-      </c>
-      <c r="D99" t="s">
-        <v>43</v>
-      </c>
-      <c r="E99" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="F99" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G99" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -6525,19 +6440,13 @@
         <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>71</v>
-      </c>
-      <c r="D100" t="s">
-        <v>71</v>
-      </c>
-      <c r="E100" t="s">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="F100" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="G100" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -6548,19 +6457,13 @@
         <v>13</v>
       </c>
       <c r="C101" t="s">
-        <v>126</v>
-      </c>
-      <c r="D101" t="s">
-        <v>126</v>
-      </c>
-      <c r="E101" t="s">
-        <v>135</v>
+        <v>58</v>
+      </c>
+      <c r="F101" t="s">
+        <v>86</v>
       </c>
       <c r="G101" t="s">
-        <v>104</v>
-      </c>
-      <c r="H101" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -6571,16 +6474,13 @@
         <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>127</v>
-      </c>
-      <c r="D102" t="s">
-        <v>127</v>
+        <v>59</v>
+      </c>
+      <c r="F102" t="s">
+        <v>75</v>
       </c>
       <c r="G102" t="s">
-        <v>103</v>
-      </c>
-      <c r="H102" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -6591,22 +6491,13 @@
         <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>128</v>
-      </c>
-      <c r="D103" t="s">
-        <v>128</v>
-      </c>
-      <c r="E103" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="F103" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="G103" t="s">
-        <v>104</v>
-      </c>
-      <c r="H103" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -6617,16 +6508,13 @@
         <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>129</v>
-      </c>
-      <c r="D104" t="s">
-        <v>129</v>
+        <v>42</v>
+      </c>
+      <c r="F104" t="s">
+        <v>69</v>
       </c>
       <c r="G104" t="s">
-        <v>103</v>
-      </c>
-      <c r="H104" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -6637,19 +6525,13 @@
         <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>72</v>
-      </c>
-      <c r="D105" t="s">
-        <v>72</v>
-      </c>
-      <c r="E105" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="F105" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="G105" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -6660,19 +6542,13 @@
         <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>130</v>
-      </c>
-      <c r="D106" t="s">
-        <v>130</v>
-      </c>
-      <c r="E106" t="s">
-        <v>137</v>
+        <v>61</v>
+      </c>
+      <c r="F106" t="s">
+        <v>75</v>
       </c>
       <c r="G106" t="s">
-        <v>104</v>
-      </c>
-      <c r="H106" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -6683,19 +6559,13 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>73</v>
-      </c>
-      <c r="D107" t="s">
-        <v>73</v>
-      </c>
-      <c r="E107" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="F107" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G107" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -6706,16 +6576,13 @@
         <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>131</v>
-      </c>
-      <c r="D108" t="s">
-        <v>131</v>
+        <v>63</v>
+      </c>
+      <c r="F108" t="s">
+        <v>69</v>
       </c>
       <c r="G108" t="s">
-        <v>103</v>
-      </c>
-      <c r="H108" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -6726,19 +6593,13 @@
         <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>132</v>
-      </c>
-      <c r="D109" t="s">
-        <v>132</v>
-      </c>
-      <c r="E109" t="s">
-        <v>77</v>
+        <v>65</v>
+      </c>
+      <c r="F109" t="s">
+        <v>89</v>
       </c>
       <c r="G109" t="s">
-        <v>104</v>
-      </c>
-      <c r="H109" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -6746,19 +6607,19 @@
         <v>3</v>
       </c>
       <c r="B110" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C110" t="s">
-        <v>133</v>
+        <v>22</v>
       </c>
       <c r="D110" t="s">
-        <v>133</v>
+        <v>22</v>
       </c>
       <c r="G110" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H110" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -6766,19 +6627,22 @@
         <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C111" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D111" t="s">
-        <v>51</v>
+        <v>23</v>
+      </c>
+      <c r="E111" t="s">
+        <v>111</v>
       </c>
       <c r="G111" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H111" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -6786,22 +6650,19 @@
         <v>3</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C112" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D112" t="s">
-        <v>52</v>
-      </c>
-      <c r="E112" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="G112" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H112" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -6809,22 +6670,19 @@
         <v>3</v>
       </c>
       <c r="B113" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C113" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>53</v>
-      </c>
-      <c r="E113" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="G113" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H113" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6832,22 +6690,22 @@
         <v>3</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C114" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D114" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="E114" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="G114" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H114" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -6855,22 +6713,19 @@
         <v>3</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C115" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="D115" t="s">
-        <v>55</v>
-      </c>
-      <c r="E115" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="G115" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H115" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -6878,22 +6733,19 @@
         <v>3</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C116" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="D116" t="s">
-        <v>56</v>
-      </c>
-      <c r="E116" t="s">
-        <v>86</v>
-      </c>
-      <c r="F116" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="G116" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="H116" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -6901,19 +6753,25 @@
         <v>3</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C117" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="D117" t="s">
-        <v>57</v>
+        <v>29</v>
+      </c>
+      <c r="E117" t="s">
+        <v>148</v>
+      </c>
+      <c r="F117" t="s">
+        <v>69</v>
       </c>
       <c r="G117" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H117" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -6921,22 +6779,25 @@
         <v>3</v>
       </c>
       <c r="B118" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C118" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D118" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="E118" t="s">
-        <v>102</v>
+        <v>148</v>
+      </c>
+      <c r="F118" t="s">
+        <v>69</v>
       </c>
       <c r="G118" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H118" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -6944,16 +6805,25 @@
         <v>3</v>
       </c>
       <c r="B119" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C119" t="s">
-        <v>67</v>
+        <v>31</v>
+      </c>
+      <c r="D119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E119" t="s">
+        <v>149</v>
       </c>
       <c r="F119" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G119" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="H119" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -6961,16 +6831,22 @@
         <v>3</v>
       </c>
       <c r="B120" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C120" t="s">
-        <v>68</v>
+        <v>51</v>
+      </c>
+      <c r="D120" t="s">
+        <v>51</v>
+      </c>
+      <c r="E120" t="s">
+        <v>150</v>
       </c>
       <c r="F120" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="G120" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -6978,16 +6854,22 @@
         <v>3</v>
       </c>
       <c r="B121" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C121" t="s">
-        <v>70</v>
-      </c>
-      <c r="F121" t="s">
-        <v>98</v>
+        <v>125</v>
+      </c>
+      <c r="D121" t="s">
+        <v>125</v>
+      </c>
+      <c r="E121" t="s">
+        <v>151</v>
       </c>
       <c r="G121" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="H121" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -6995,16 +6877,22 @@
         <v>3</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C122" t="s">
-        <v>74</v>
-      </c>
-      <c r="F122" t="s">
-        <v>101</v>
+        <v>126</v>
+      </c>
+      <c r="D122" t="s">
+        <v>126</v>
+      </c>
+      <c r="E122" t="s">
+        <v>152</v>
       </c>
       <c r="G122" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="H122" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -7012,16 +6900,22 @@
         <v>3</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C123" t="s">
-        <v>75</v>
-      </c>
-      <c r="F123" t="s">
-        <v>85</v>
+        <v>127</v>
+      </c>
+      <c r="D123" t="s">
+        <v>127</v>
+      </c>
+      <c r="E123" t="s">
+        <v>153</v>
       </c>
       <c r="G123" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="H123" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -7029,16 +6923,22 @@
         <v>3</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C124" t="s">
-        <v>47</v>
+        <v>52</v>
+      </c>
+      <c r="D124" t="s">
+        <v>52</v>
+      </c>
+      <c r="E124" t="s">
+        <v>154</v>
       </c>
       <c r="F124" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G124" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -7046,16 +6946,19 @@
         <v>3</v>
       </c>
       <c r="B125" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C125" t="s">
-        <v>48</v>
-      </c>
-      <c r="F125" t="s">
-        <v>79</v>
+        <v>128</v>
+      </c>
+      <c r="D125" t="s">
+        <v>128</v>
       </c>
       <c r="G125" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="H125" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -7063,16 +6966,22 @@
         <v>3</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C126" t="s">
-        <v>49</v>
-      </c>
-      <c r="F126" t="s">
-        <v>93</v>
+        <v>129</v>
+      </c>
+      <c r="D126" t="s">
+        <v>129</v>
+      </c>
+      <c r="E126" t="s">
+        <v>75</v>
       </c>
       <c r="G126" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="H126" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -7080,16 +6989,19 @@
         <v>3</v>
       </c>
       <c r="B127" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C127" t="s">
-        <v>76</v>
-      </c>
-      <c r="F127" t="s">
-        <v>102</v>
+        <v>130</v>
+      </c>
+      <c r="D127" t="s">
+        <v>130</v>
       </c>
       <c r="G127" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="H127" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -7100,16 +7012,19 @@
         <v>14</v>
       </c>
       <c r="C128" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="D128" t="s">
-        <v>22</v>
+        <v>131</v>
+      </c>
+      <c r="E128" t="s">
+        <v>111</v>
       </c>
       <c r="G128" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H128" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -7120,19 +7035,19 @@
         <v>14</v>
       </c>
       <c r="C129" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="D129" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="E129" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G129" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H129" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -7143,16 +7058,16 @@
         <v>14</v>
       </c>
       <c r="C130" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D130" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G130" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H130" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -7163,16 +7078,16 @@
         <v>14</v>
       </c>
       <c r="C131" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D131" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G131" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H131" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -7183,19 +7098,19 @@
         <v>14</v>
       </c>
       <c r="C132" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D132" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E132" t="s">
-        <v>78</v>
+        <v>69</v>
+      </c>
+      <c r="F132" t="s">
+        <v>69</v>
       </c>
       <c r="G132" t="s">
-        <v>104</v>
-      </c>
-      <c r="H132" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -7206,16 +7121,19 @@
         <v>14</v>
       </c>
       <c r="C133" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D133" t="s">
-        <v>27</v>
+        <v>36</v>
+      </c>
+      <c r="E133" t="s">
+        <v>69</v>
+      </c>
+      <c r="F133" t="s">
+        <v>69</v>
       </c>
       <c r="G133" t="s">
-        <v>103</v>
-      </c>
-      <c r="H133" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -7226,19 +7144,19 @@
         <v>14</v>
       </c>
       <c r="C134" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D134" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E134" t="s">
-        <v>77</v>
+        <v>155</v>
+      </c>
+      <c r="F134" t="s">
+        <v>78</v>
       </c>
       <c r="G134" t="s">
-        <v>104</v>
-      </c>
-      <c r="H134" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -7249,19 +7167,19 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D135" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E135" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="F135" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G135" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -7272,19 +7190,19 @@
         <v>14</v>
       </c>
       <c r="C136" t="s">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="D136" t="s">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="E136" t="s">
-        <v>79</v>
-      </c>
-      <c r="F136" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="G136" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H136" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -7295,19 +7213,19 @@
         <v>14</v>
       </c>
       <c r="C137" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="D137" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="E137" t="s">
-        <v>150</v>
-      </c>
-      <c r="F137" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="G137" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H137" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -7318,19 +7236,19 @@
         <v>14</v>
       </c>
       <c r="C138" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="D138" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="E138" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="G138" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H138" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -7341,16 +7259,22 @@
         <v>14</v>
       </c>
       <c r="C139" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="D139" t="s">
-        <v>33</v>
+        <v>136</v>
+      </c>
+      <c r="E139" t="s">
+        <v>159</v>
+      </c>
+      <c r="F139" t="s">
+        <v>165</v>
       </c>
       <c r="G139" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H139" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -7361,19 +7285,16 @@
         <v>14</v>
       </c>
       <c r="C140" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="D140" t="s">
-        <v>34</v>
-      </c>
-      <c r="E140" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="G140" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H140" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -7384,19 +7305,19 @@
         <v>14</v>
       </c>
       <c r="C141" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D141" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E141" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F141" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G141" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -7407,19 +7328,16 @@
         <v>14</v>
       </c>
       <c r="C142" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="D142" t="s">
-        <v>36</v>
-      </c>
-      <c r="E142" t="s">
-        <v>79</v>
-      </c>
-      <c r="F142" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="G142" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="H142" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -7430,19 +7348,19 @@
         <v>14</v>
       </c>
       <c r="C143" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="D143" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="E143" t="s">
-        <v>82</v>
-      </c>
-      <c r="F143" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="G143" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H143" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -7453,19 +7371,19 @@
         <v>14</v>
       </c>
       <c r="C144" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D144" t="s">
-        <v>38</v>
-      </c>
-      <c r="E144" t="s">
-        <v>81</v>
+        <v>54</v>
+      </c>
+      <c r="F144" t="s">
+        <v>83</v>
       </c>
       <c r="G144" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H144" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -7482,10 +7400,10 @@
         <v>39</v>
       </c>
       <c r="G145" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H145" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -7501,14 +7419,11 @@
       <c r="D146" t="s">
         <v>40</v>
       </c>
-      <c r="E146" t="s">
-        <v>77</v>
-      </c>
       <c r="G146" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H146" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -7525,13 +7440,13 @@
         <v>41</v>
       </c>
       <c r="E147" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F147" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G147" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -7548,13 +7463,13 @@
         <v>42</v>
       </c>
       <c r="E148" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F148" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G148" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -7571,13 +7486,13 @@
         <v>43</v>
       </c>
       <c r="E149" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="F149" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="G149" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -7588,19 +7503,19 @@
         <v>14</v>
       </c>
       <c r="C150" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D150" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E150" t="s">
-        <v>81</v>
+        <v>161</v>
+      </c>
+      <c r="F150" t="s">
+        <v>85</v>
       </c>
       <c r="G150" t="s">
-        <v>104</v>
-      </c>
-      <c r="H150" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -7611,16 +7526,19 @@
         <v>14</v>
       </c>
       <c r="C151" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="D151" t="s">
-        <v>45</v>
+        <v>140</v>
+      </c>
+      <c r="E151" t="s">
+        <v>151</v>
       </c>
       <c r="G151" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H151" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -7631,19 +7549,19 @@
         <v>14</v>
       </c>
       <c r="C152" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="D152" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="E152" t="s">
-        <v>77</v>
+        <v>162</v>
       </c>
       <c r="G152" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H152" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -7654,19 +7572,19 @@
         <v>14</v>
       </c>
       <c r="C153" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="D153" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="E153" t="s">
-        <v>79</v>
-      </c>
-      <c r="F153" t="s">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="G153" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H153" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -7677,19 +7595,22 @@
         <v>14</v>
       </c>
       <c r="C154" t="s">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="D154" t="s">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="E154" t="s">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="F154" t="s">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="G154" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="H154" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -7700,19 +7621,16 @@
         <v>14</v>
       </c>
       <c r="C155" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="D155" t="s">
-        <v>49</v>
-      </c>
-      <c r="E155" t="s">
-        <v>151</v>
-      </c>
-      <c r="F155" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="G155" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="H155" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -7723,19 +7641,19 @@
         <v>14</v>
       </c>
       <c r="C156" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D156" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E156" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="F156" t="s">
+        <v>75</v>
       </c>
       <c r="G156" t="s">
-        <v>104</v>
-      </c>
-      <c r="H156" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -7746,16 +7664,16 @@
         <v>14</v>
       </c>
       <c r="C157" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D157" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G157" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H157" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -7766,19 +7684,19 @@
         <v>14</v>
       </c>
       <c r="C158" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D158" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E158" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="G158" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H158" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -7789,19 +7707,16 @@
         <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D159" t="s">
-        <v>146</v>
-      </c>
-      <c r="E159" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="G159" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H159" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -7812,19 +7727,16 @@
         <v>14</v>
       </c>
       <c r="C160" t="s">
-        <v>147</v>
+        <v>45</v>
       </c>
       <c r="D160" t="s">
-        <v>147</v>
-      </c>
-      <c r="E160" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="G160" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H160" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -7835,19 +7747,16 @@
         <v>14</v>
       </c>
       <c r="C161" t="s">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="D161" t="s">
-        <v>148</v>
-      </c>
-      <c r="E161" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="G161" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H161" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -7858,19 +7767,19 @@
         <v>14</v>
       </c>
       <c r="C162" t="s">
-        <v>149</v>
+        <v>47</v>
       </c>
       <c r="D162" t="s">
-        <v>149</v>
+        <v>47</v>
       </c>
       <c r="E162" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="G162" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H162" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -7881,16 +7790,19 @@
         <v>14</v>
       </c>
       <c r="C163" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D163" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="E163" t="s">
+        <v>75</v>
       </c>
       <c r="G163" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H163" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -7901,19 +7813,19 @@
         <v>14</v>
       </c>
       <c r="C164" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E164" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G164" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H164" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -7924,19 +7836,22 @@
         <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D165" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E165" t="s">
-        <v>79</v>
+        <v>164</v>
+      </c>
+      <c r="F165" t="s">
+        <v>76</v>
       </c>
       <c r="G165" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H165" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -7947,19 +7862,13 @@
         <v>14</v>
       </c>
       <c r="C166" t="s">
-        <v>54</v>
-      </c>
-      <c r="D166" t="s">
-        <v>54</v>
-      </c>
-      <c r="E166" t="s">
-        <v>85</v>
+        <v>29</v>
+      </c>
+      <c r="F166" t="s">
+        <v>69</v>
       </c>
       <c r="G166" t="s">
-        <v>104</v>
-      </c>
-      <c r="H166" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -7970,19 +7879,13 @@
         <v>14</v>
       </c>
       <c r="C167" t="s">
-        <v>55</v>
-      </c>
-      <c r="D167" t="s">
-        <v>55</v>
-      </c>
-      <c r="E167" t="s">
-        <v>78</v>
+        <v>30</v>
+      </c>
+      <c r="F167" t="s">
+        <v>69</v>
       </c>
       <c r="G167" t="s">
-        <v>104</v>
-      </c>
-      <c r="H167" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -7993,19 +7896,13 @@
         <v>14</v>
       </c>
       <c r="C168" t="s">
-        <v>56</v>
-      </c>
-      <c r="D168" t="s">
-        <v>56</v>
-      </c>
-      <c r="E168" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="F168" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G168" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -8016,13 +7913,13 @@
         <v>14</v>
       </c>
       <c r="C169" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="F169" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G169" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -8033,13 +7930,13 @@
         <v>14</v>
       </c>
       <c r="C170" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F170" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G170" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -8050,13 +7947,13 @@
         <v>14</v>
       </c>
       <c r="C171" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F171" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G171" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -8067,13 +7964,13 @@
         <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F172" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G172" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -8084,13 +7981,13 @@
         <v>14</v>
       </c>
       <c r="C173" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F173" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G173" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -8101,13 +7998,13 @@
         <v>14</v>
       </c>
       <c r="C174" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F174" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="G174" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -8118,13 +8015,13 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F175" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G175" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -8135,13 +8032,13 @@
         <v>14</v>
       </c>
       <c r="C176" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F176" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G176" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -8152,13 +8049,13 @@
         <v>14</v>
       </c>
       <c r="C177" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F177" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G177" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -8169,47 +8066,13 @@
         <v>14</v>
       </c>
       <c r="C178" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="F178" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G178" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
-      <c r="A179">
-        <v>3</v>
-      </c>
-      <c r="B179" t="s">
-        <v>14</v>
-      </c>
-      <c r="C179" t="s">
-        <v>75</v>
-      </c>
-      <c r="F179" t="s">
-        <v>85</v>
-      </c>
-      <c r="G179" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
-      <c r="A180">
-        <v>3</v>
-      </c>
-      <c r="B180" t="s">
-        <v>14</v>
-      </c>
-      <c r="C180" t="s">
-        <v>76</v>
-      </c>
-      <c r="F180" t="s">
-        <v>102</v>
-      </c>
-      <c r="G180" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/rda-experiments/runs/v10-sample3/evaluation_results.xlsx
+++ b/notebooks/rda-experiments/runs/v10-sample3/evaluation_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="152">
   <si>
     <t>fields in reference</t>
   </si>
@@ -155,6 +155,24 @@
     <t>dmp.dataset[2].type</t>
   </si>
   <si>
+    <t>dmp.dataset[3].dataset_id.identifier</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].dataset_id.type</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].personal_data</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].sensitive_data</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].title</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].type</t>
+  </si>
+  <si>
     <t>dmp.dmp_id.identifier</t>
   </si>
   <si>
@@ -173,6 +191,30 @@
     <t>dmp.title</t>
   </si>
   <si>
+    <t>dmp.project[0].title</t>
+  </si>
+  <si>
+    <t>dmp.project[0].description</t>
+  </si>
+  <si>
+    <t>dmp.project[0].funding[0].funder_id.identifier</t>
+  </si>
+  <si>
+    <t>dmp.project[0].funding[0].funder_id.type</t>
+  </si>
+  <si>
+    <t>dmp.project[0].funding[0].funding_status</t>
+  </si>
+  <si>
+    <t>dmp.related_identifier[0].identifier</t>
+  </si>
+  <si>
+    <t>dmp.related_identifier[0].relation_type</t>
+  </si>
+  <si>
+    <t>dmp.related_identifier[0].type</t>
+  </si>
+  <si>
     <t>dmp.dataset[0].description</t>
   </si>
   <si>
@@ -206,22 +248,10 @@
     <t>dmp.dataset[3].metadata[0].language</t>
   </si>
   <si>
-    <t>dmp.dataset[3].personal_data</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].sensitive_data</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].title</t>
-  </si>
-  <si>
     <t>dmp.description</t>
   </si>
   <si>
-    <t>0000-0003-0644-4174</t>
-  </si>
-  <si>
-    <t>orcid</t>
+    <t>other</t>
   </si>
   <si>
     <t>2026-10-19T00:00:00Z</t>
@@ -242,73 +272,184 @@
     <t>Simulation code for controller development and testing</t>
   </si>
   <si>
+    <t>Software generated under the project</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>CPS 2015</t>
+  </si>
+  <si>
+    <t>The project aims to manage and disseminate data generated by the project.</t>
+  </si>
+  <si>
+    <t>planned</t>
+  </si>
+  <si>
+    <t>isPartOf</t>
+  </si>
+  <si>
+    <t>data related to each of our proposed experiments</t>
+  </si>
+  <si>
+    <t>code and results for all analyses completed on experimental data</t>
+  </si>
+  <si>
+    <t>simulation code for controller development and testing</t>
+  </si>
+  <si>
+    <t>videos of the experiments</t>
+  </si>
+  <si>
+    <t>First, we will have data related to each of our proposed experiments. These will include the detailed protocols used for each experiment, the raw data collected from each experiment, and the experimental code used to collect those data. The relevant code will include both the data acquisition code, and the code for the controllers used in the experiment. Together, this information will be sufficient for recreating the circumstances of each data collection session.</t>
+  </si>
+  <si>
+    <t>servers at the Rehabilitation Institute of Chicago</t>
+  </si>
+  <si>
+    <t>Our second type of data will be the code and results for all analyses completed on experimental data. Specifically, we store all code necessary to recreate figures, tables, and other results reported in all published manuscripts.</t>
+  </si>
+  <si>
+    <t>The contents of each data file, including the experimental conditions or the analysis procedures used during generation will be documented.</t>
+  </si>
+  <si>
+    <t>The code needed to generate all published results will be documented clearly.</t>
+  </si>
+  <si>
+    <t>The proposed foundational developments will produce substantial simulation code for controller development and testing. These and the outputs relevant to all key findings will also be managed.</t>
+  </si>
+  <si>
+    <t>GNU Public License</t>
+  </si>
+  <si>
+    <t>Select videos of the experiments will be distributed, with subject faces blurred so as to be unidentifiable.</t>
+  </si>
+  <si>
+    <t>We will manage all scientific and technical content generated from this proposal. Our products will include 3 broad types of data.</t>
+  </si>
+  <si>
+    <t>Correct</t>
+  </si>
+  <si>
+    <t>Hallucinated</t>
+  </si>
+  <si>
+    <t>Missed</t>
+  </si>
+  <si>
+    <t>both empty</t>
+  </si>
+  <si>
+    <t>not in the reference</t>
+  </si>
+  <si>
+    <t>only 20% of the model's words are in the reference</t>
+  </si>
+  <si>
+    <t>dmp.dataset[0].distribution[0].data_access</t>
+  </si>
+  <si>
+    <t>dmp.dataset[0].distribution[0].title</t>
+  </si>
+  <si>
+    <t>dmp.dataset[0].distribution[0].host.url</t>
+  </si>
+  <si>
+    <t>dmp.dataset[0].distribution[0].license[0].license_ref</t>
+  </si>
+  <si>
+    <t>dmp.dataset[0].distribution[0].license[0].start_date</t>
+  </si>
+  <si>
+    <t>dmp.dataset[0].metadata[0].language</t>
+  </si>
+  <si>
+    <t>dmp.dataset[0].metadata[0].metadata_standard_id[0].identifier</t>
+  </si>
+  <si>
+    <t>dmp.dataset[0].metadata[0].metadata_standard_id[0].type</t>
+  </si>
+  <si>
+    <t>dmp.dataset[0].metadata[0].description</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].distribution[0].data_access</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].distribution[0].title</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].distribution[0].host.title</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].distribution[0].host.url</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].distribution[0].license[0].license_ref</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].distribution[0].license[0].start_date</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].metadata[0].metadata_standard_id[0].identifier</t>
+  </si>
+  <si>
+    <t>dmp.dataset[1].metadata[0].metadata_standard_id[0].type</t>
+  </si>
+  <si>
+    <t>dmp.dataset[2].distribution[0].data_access</t>
+  </si>
+  <si>
+    <t>dmp.dataset[2].distribution[0].title</t>
+  </si>
+  <si>
+    <t>dmp.dataset[2].distribution[0].host.title</t>
+  </si>
+  <si>
+    <t>dmp.dataset[2].distribution[0].host.url</t>
+  </si>
+  <si>
+    <t>dmp.dataset[2].distribution[0].license[0].start_date</t>
+  </si>
+  <si>
+    <t>dmp.dataset[2].metadata[0].metadata_standard_id[0].identifier</t>
+  </si>
+  <si>
+    <t>dmp.dataset[2].metadata[0].metadata_standard_id[0].type</t>
+  </si>
+  <si>
+    <t>dmp.dataset[2].metadata[0].description</t>
+  </si>
+  <si>
+    <t>These will include the detailed protocols used for each experiment, the raw data collected from each experiment, and the experimental code used to collect those data. The relevant code will include both the data acquisition code, and the code for the controllers used in the experiment. Together, this information will be sufficient for recreating the circumstances of each data collection session.</t>
+  </si>
+  <si>
+    <t>shared</t>
+  </si>
+  <si>
+    <t>Rehabilitation Institute of Chicago</t>
+  </si>
+  <si>
+    <t>2026-10-19</t>
+  </si>
+  <si>
+    <t>Specifically, we store all code necessary to recreate figures, tables, and other results reported in all published manuscripts. The proposed foundational developments will produce substantial simulation code for controller development and testing. These and the outputs relevant to all key findings will also be managed.</t>
+  </si>
+  <si>
+    <t>These and the outputs relevant to all key findings will also be managed.</t>
+  </si>
+  <si>
     <t>unknown</t>
   </si>
   <si>
-    <t>eng</t>
-  </si>
-  <si>
-    <t>CPS 2015</t>
-  </si>
-  <si>
-    <t>data related to each of our proposed experiments</t>
-  </si>
-  <si>
-    <t>code and results for all analyses completed on experimental data</t>
-  </si>
-  <si>
-    <t>simulation code for controller development and testing</t>
-  </si>
-  <si>
-    <t>First, we will have data related to each of our proposed experiments. These will include the detailed protocols used for each experiment, the raw data collected from each experiment, and the experimental code used to collect those data. The relevant code will include both the data acquisition code, and the code for the controllers used in the experiment. Together, this information will be sufficient for recreating the circumstances of each data collection session.</t>
-  </si>
-  <si>
-    <t>servers at the Rehabilitation Institute of Chicago</t>
-  </si>
-  <si>
-    <t>Our second type of data will be the code and results for all analyses completed on experimental data. Specifically, we store all code necessary to recreate figures, tables, and other results reported in all published manuscripts.</t>
-  </si>
-  <si>
-    <t>The contents of each data file, including the experimental conditions or the analysis procedures used during generation will be documented.</t>
-  </si>
-  <si>
-    <t>The code needed to generate all published results will be documented clearly.</t>
-  </si>
-  <si>
-    <t>The proposed foundational developments will produce substantial simulation code for controller development and testing. These and the outputs relevant to all key findings will also be managed.</t>
-  </si>
-  <si>
-    <t>GNU Public License</t>
-  </si>
-  <si>
-    <t>Select videos of the experiments will be distributed, with subject faces blurred so as to be unidentifiable.</t>
-  </si>
-  <si>
-    <t>videos of the experiments</t>
-  </si>
-  <si>
-    <t>We will manage all scientific and technical content generated from this proposal. Our products will include 3 broad types of data.</t>
-  </si>
-  <si>
-    <t>Hallucinated</t>
-  </si>
-  <si>
-    <t>Correct</t>
-  </si>
-  <si>
-    <t>Missed</t>
-  </si>
-  <si>
-    <t>not in the reference</t>
-  </si>
-  <si>
-    <t>both empty</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].dataset_id.identifier</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].dataset_id.type</t>
+    <t>null</t>
+  </si>
+  <si>
+    <t>only 57% of the model's words are in the reference</t>
+  </si>
+  <si>
+    <t>empty where the reference has a value</t>
   </si>
   <si>
     <t>dmp.dataset[4].dataset_id.identifier</t>
@@ -326,205 +467,13 @@
     <t>dmp.dataset[4].title</t>
   </si>
   <si>
-    <t>dmp.dataset[4].description</t>
-  </si>
-  <si>
-    <t>dmp.dataset[5].dataset_id.identifier</t>
-  </si>
-  <si>
-    <t>dmp.dataset[5].dataset_id.type</t>
-  </si>
-  <si>
-    <t>dmp.dataset[5].personal_data</t>
-  </si>
-  <si>
-    <t>dmp.dataset[5].sensitive_data</t>
-  </si>
-  <si>
-    <t>dmp.dataset[5].title</t>
-  </si>
-  <si>
-    <t>dmp.dataset[5].description</t>
-  </si>
-  <si>
-    <t>dmp.project[0].title</t>
-  </si>
-  <si>
-    <t>dmp.project[0].description</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>These will include the detailed protocols used for each experiment, the raw data collected from each experiment, and the experimental code used to collect those data. The relevant code will include both the data acquisition code, and the code for the controllers used in the experiment. Together, this information will be sufficient for recreating the circumstances of each data collection session.</t>
-  </si>
-  <si>
-    <t>We store all code necessary to recreate figures, tables, and other results reported in all published manuscripts. The proposed foundational developments will produce substantial simulation code for controller development and testing. These and the outputs relevant to all key findings will also be managed.</t>
-  </si>
-  <si>
-    <t>experimental analyses results</t>
-  </si>
-  <si>
-    <t>Experimental analyses results will be made available through peer-reviewed journal publications and conference presentations.</t>
-  </si>
-  <si>
-    <t>software generated under the project</t>
-  </si>
-  <si>
-    <t>Software generated under the project will be released under the GNU Public License, and available for free download on the labs’ websites. This includes code for each of our 3 experimental systems.</t>
-  </si>
-  <si>
-    <t>raw data files</t>
-  </si>
-  <si>
-    <t>Raw data files will be saved in either Matlab or comma-separated value (CSV) format. The contents of each data file, including the experimental conditions or the analysis procedures used during generation will be documented. All raw data will be de-identified to ensure subject anonynimity.</t>
-  </si>
-  <si>
-    <t>The Data Management Plan should clearly articulate how the PI and co-PIs plan to manage and disseminate data generated by the project. The plan should outline the rights and obligations of all parties as to their roles and responsibilities in the management and retention of research data, and consider changes that would occur should a PI or co-PI leave the institution or project. Any costs should be explained in the Budget Justification pages. Data will be generated at each of our institutional sites. The PI at each institution will be responsible for following the data management guidelines described below, and for saving the data to the RIC servers. This process of transferring all data to a central location will be facilitated by our research project coordinator. Our data management guidelines will be reviewed at the kickoff meeting for the project, and revisited briefly at each of our quarterly meetings with the PIs.</t>
-  </si>
-  <si>
-    <t>only 56% of the model's words are in the reference</t>
-  </si>
-  <si>
-    <t>different value</t>
-  </si>
-  <si>
-    <t>only 0% of the model's words are in the reference</t>
-  </si>
-  <si>
-    <t>only 20% of the model's words are in the reference</t>
-  </si>
-  <si>
-    <t>dmp.dataset[0].distribution[0].data_access</t>
-  </si>
-  <si>
-    <t>dmp.dataset[0].distribution[0].title</t>
-  </si>
-  <si>
-    <t>dmp.dataset[0].distribution[0].description</t>
-  </si>
-  <si>
-    <t>dmp.dataset[0].distribution[0].host.url</t>
-  </si>
-  <si>
-    <t>dmp.dataset[0].metadata[0].language</t>
-  </si>
-  <si>
-    <t>dmp.dataset[0].metadata[0].metadata_standard_id[0].identifier</t>
-  </si>
-  <si>
-    <t>dmp.dataset[0].metadata[0].metadata_standard_id[0].type</t>
-  </si>
-  <si>
-    <t>dmp.dataset[0].metadata[0].description</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].distribution[0].data_access</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].distribution[0].title</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].distribution[0].description</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].distribution[0].host.title</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].distribution[0].host.url</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].metadata[0].metadata_standard_id[0].identifier</t>
-  </si>
-  <si>
-    <t>dmp.dataset[1].metadata[0].metadata_standard_id[0].type</t>
-  </si>
-  <si>
-    <t>dmp.dataset[2].distribution[0].data_access</t>
-  </si>
-  <si>
-    <t>dmp.dataset[2].distribution[0].title</t>
-  </si>
-  <si>
-    <t>dmp.dataset[2].distribution[0].description</t>
-  </si>
-  <si>
-    <t>dmp.dataset[2].distribution[0].host.title</t>
-  </si>
-  <si>
-    <t>dmp.dataset[2].distribution[0].host.url</t>
-  </si>
-  <si>
-    <t>dmp.dataset[2].metadata[0].metadata_standard_id[0].identifier</t>
-  </si>
-  <si>
-    <t>dmp.dataset[2].metadata[0].metadata_standard_id[0].type</t>
-  </si>
-  <si>
-    <t>dmp.dataset[2].metadata[0].description</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Experimental data</t>
-  </si>
-  <si>
-    <t>Data related to each of our proposed experiments. These will include the detailed protocols used for each experiment, the raw data collected from each experiment, and the experimental code used to collect those data.</t>
-  </si>
-  <si>
-    <t>shared</t>
-  </si>
-  <si>
-    <t>Experimental data distribution</t>
-  </si>
-  <si>
-    <t>Data will be made available upon request, after the conclusion of each of study.</t>
-  </si>
-  <si>
-    <t>Rehabilitation Institute of Chicago servers</t>
-  </si>
-  <si>
-    <t>Analysis code and results</t>
-  </si>
-  <si>
-    <t>Code and results for all analyses completed on experimental data.</t>
-  </si>
-  <si>
-    <t>Analysis code and results distribution</t>
-  </si>
-  <si>
-    <t>Code needed to generate all published results will be documented clearly.</t>
-  </si>
-  <si>
-    <t>Project website</t>
-  </si>
-  <si>
-    <t>Simulation code</t>
-  </si>
-  <si>
-    <t>Substantial simulation code for controller development and testing.</t>
-  </si>
-  <si>
-    <t>Simulation code distribution</t>
-  </si>
-  <si>
-    <t>Software generated under the project will be released under the GNU Public License.</t>
-  </si>
-  <si>
-    <t>CPS 2015 Data Management Plan</t>
-  </si>
-  <si>
-    <t>null</t>
-  </si>
-  <si>
-    <t>only 50% of the model's words are in the reference</t>
-  </si>
-  <si>
-    <t>empty where the reference has a value</t>
-  </si>
-  <si>
-    <t>only 40% of the model's words are in the reference</t>
+    <t>dmp.dataset[4].type</t>
+  </si>
+  <si>
+    <t>Data related to proposed experiments</t>
+  </si>
+  <si>
+    <t>Select videos of the experiments</t>
   </si>
 </sst>
 </file>
@@ -931,34 +880,34 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0.6899999999999999</v>
+        <v>0.512</v>
       </c>
       <c r="H2">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="I2">
-        <v>0.506</v>
+        <v>0.495</v>
       </c>
       <c r="J2">
-        <v>0.4545454545454545</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="K2">
-        <v>0.2045454545454546</v>
+        <v>0.375</v>
       </c>
       <c r="L2">
-        <v>0.3409090909090909</v>
+        <v>0.2321428571428572</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -969,34 +918,34 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D3">
+        <v>34</v>
+      </c>
+      <c r="E3">
         <v>27</v>
       </c>
-      <c r="E3">
-        <v>22</v>
-      </c>
       <c r="F3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>0.551</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H3">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="I3">
-        <v>0.464</v>
+        <v>0.596</v>
       </c>
       <c r="J3">
-        <v>0.421875</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="K3">
-        <v>0.34375</v>
+        <v>0.3857142857142857</v>
       </c>
       <c r="L3">
-        <v>0.234375</v>
+        <v>0.1285714285714286</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1007,34 +956,34 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>0.536</v>
+        <v>0.537</v>
       </c>
       <c r="H4">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="I4">
-        <v>0.506</v>
+        <v>0.528</v>
       </c>
       <c r="J4">
-        <v>0.4347826086956522</v>
+        <v>0.4150943396226415</v>
       </c>
       <c r="K4">
-        <v>0.3768115942028986</v>
+        <v>0.3584905660377358</v>
       </c>
       <c r="L4">
-        <v>0.1884057971014493</v>
+        <v>0.2264150943396226</v>
       </c>
     </row>
   </sheetData>
@@ -1044,7 +993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1080,14 +1029,11 @@
       <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>66</v>
-      </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1101,13 +1047,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1121,10 +1067,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1138,10 +1084,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1155,13 +1101,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1175,10 +1121,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1191,11 +1137,14 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1209,13 +1158,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1229,13 +1178,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1249,13 +1198,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1269,13 +1218,13 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1289,10 +1238,10 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1305,11 +1254,14 @@
       <c r="C14" t="s">
         <v>34</v>
       </c>
+      <c r="D14" t="s">
+        <v>77</v>
+      </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1323,13 +1275,13 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1343,13 +1295,13 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1363,13 +1315,13 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1383,13 +1335,13 @@
         <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1403,10 +1355,10 @@
         <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G19" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1419,11 +1371,14 @@
       <c r="C20" t="s">
         <v>40</v>
       </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
       <c r="F20" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1437,13 +1392,13 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1457,13 +1412,13 @@
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1477,13 +1432,13 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1497,13 +1452,13 @@
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1517,10 +1472,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1533,11 +1488,14 @@
       <c r="C26" t="s">
         <v>46</v>
       </c>
+      <c r="D26" t="s">
+        <v>77</v>
+      </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1551,13 +1509,13 @@
         <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>79</v>
+      </c>
+      <c r="E27" t="s">
+        <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1571,13 +1529,13 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
+        <v>79</v>
+      </c>
+      <c r="E28" t="s">
+        <v>79</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1591,13 +1549,16 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>84</v>
+      </c>
+      <c r="E29" t="s">
+        <v>93</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G29" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1611,13 +1572,13 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="G30" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1627,11 +1588,14 @@
       <c r="B31" t="s">
         <v>51</v>
       </c>
-      <c r="E31" t="s">
-        <v>80</v>
+      <c r="C31" t="s">
+        <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="G31" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1641,182 +1605,254 @@
       <c r="B32" t="s">
         <v>52</v>
       </c>
-      <c r="E32" t="s">
-        <v>81</v>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" t="s">
+        <v>77</v>
       </c>
       <c r="F32" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
       <c r="B33" t="s">
         <v>53</v>
       </c>
-      <c r="E33" t="s">
-        <v>82</v>
+      <c r="C33" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" t="s">
+        <v>79</v>
       </c>
       <c r="F33" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
       </c>
-      <c r="E34" t="s">
-        <v>83</v>
+      <c r="C34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" t="s">
+        <v>85</v>
       </c>
       <c r="F34" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
       <c r="B35" t="s">
         <v>55</v>
       </c>
-      <c r="E35" t="s">
-        <v>75</v>
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
+        <v>78</v>
       </c>
       <c r="F35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G35" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
       <c r="B36" t="s">
         <v>56</v>
       </c>
+      <c r="C36" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" t="s">
+        <v>86</v>
+      </c>
       <c r="E36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F36" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
       <c r="B37" t="s">
         <v>57</v>
       </c>
-      <c r="E37" t="s">
-        <v>85</v>
+      <c r="C37" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" t="s">
+        <v>86</v>
       </c>
       <c r="F37" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
       <c r="B38" t="s">
         <v>58</v>
       </c>
-      <c r="E38" t="s">
-        <v>86</v>
+      <c r="C38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" t="s">
+        <v>87</v>
       </c>
       <c r="F38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G38" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>3</v>
       </c>
       <c r="B39" t="s">
         <v>59</v>
       </c>
-      <c r="E39" t="s">
-        <v>75</v>
+      <c r="C39" t="s">
+        <v>59</v>
       </c>
       <c r="F39" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>103</v>
+      </c>
+      <c r="G39" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>3</v>
       </c>
       <c r="B40" t="s">
         <v>60</v>
       </c>
-      <c r="E40" t="s">
-        <v>87</v>
+      <c r="C40" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" t="s">
+        <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>3</v>
       </c>
       <c r="B41" t="s">
         <v>61</v>
       </c>
-      <c r="E41" t="s">
-        <v>75</v>
+      <c r="C41" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" t="s">
+        <v>88</v>
       </c>
       <c r="F41" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G41" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>3</v>
       </c>
       <c r="B42" t="s">
         <v>62</v>
       </c>
-      <c r="E42" t="s">
-        <v>69</v>
+      <c r="C42" t="s">
+        <v>62</v>
       </c>
       <c r="F42" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>103</v>
+      </c>
+      <c r="G42" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>3</v>
       </c>
       <c r="B43" t="s">
         <v>63</v>
       </c>
-      <c r="E43" t="s">
-        <v>69</v>
+      <c r="C43" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" t="s">
+        <v>89</v>
       </c>
       <c r="F43" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G43" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>3</v>
       </c>
       <c r="B44" t="s">
         <v>64</v>
       </c>
-      <c r="E44" t="s">
-        <v>88</v>
+      <c r="C44" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" t="s">
+        <v>77</v>
       </c>
       <c r="F44" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G44" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>3</v>
       </c>
@@ -1824,10 +1860,178 @@
         <v>65</v>
       </c>
       <c r="E45" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F45" t="s">
-        <v>92</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46" t="s">
+        <v>66</v>
+      </c>
+      <c r="E46" t="s">
+        <v>95</v>
+      </c>
+      <c r="F46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" t="s">
+        <v>96</v>
+      </c>
+      <c r="F47" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>3</v>
+      </c>
+      <c r="B48" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>3</v>
+      </c>
+      <c r="B49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" t="s">
+        <v>98</v>
+      </c>
+      <c r="F50" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51" t="s">
+        <v>99</v>
+      </c>
+      <c r="F51" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>3</v>
+      </c>
+      <c r="B52" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" t="s">
+        <v>100</v>
+      </c>
+      <c r="F52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" t="s">
+        <v>85</v>
+      </c>
+      <c r="F53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s">
+        <v>74</v>
+      </c>
+      <c r="E54" t="s">
+        <v>101</v>
+      </c>
+      <c r="F54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>3</v>
+      </c>
+      <c r="B55" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" t="s">
+        <v>85</v>
+      </c>
+      <c r="F55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s">
+        <v>49</v>
+      </c>
+      <c r="E56" t="s">
+        <v>93</v>
+      </c>
+      <c r="F56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="E57" t="s">
+        <v>102</v>
+      </c>
+      <c r="F57" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1837,7 +2041,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1874,10 +2078,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1891,13 +2095,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1911,10 +2115,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1928,10 +2132,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1945,13 +2149,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1965,10 +2169,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1981,11 +2185,14 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1999,13 +2206,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2019,13 +2226,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2039,13 +2246,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2053,19 +2260,19 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2073,16 +2280,19 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>109</v>
+      </c>
+      <c r="D13" t="s">
+        <v>135</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2090,16 +2300,16 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G14" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2107,19 +2317,19 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="F15" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2127,19 +2337,16 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="F16" t="s">
-        <v>91</v>
+        <v>103</v>
+      </c>
+      <c r="G16" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2147,19 +2354,19 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="G17" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2167,22 +2374,19 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="F18" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2190,16 +2394,19 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>114</v>
+      </c>
+      <c r="D19" t="s">
+        <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G19" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2207,16 +2414,16 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="F20" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2224,22 +2431,19 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G21" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2247,22 +2451,19 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="F22" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G22" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2270,19 +2471,16 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>103</v>
+      </c>
+      <c r="G23" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2290,19 +2488,19 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F24" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="G24" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2310,16 +2508,19 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>35</v>
+      </c>
+      <c r="D25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" t="s">
+        <v>79</v>
       </c>
       <c r="F25" t="s">
-        <v>91</v>
-      </c>
-      <c r="G25" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2327,16 +2528,19 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>36</v>
+      </c>
+      <c r="D26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" t="s">
+        <v>79</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
-      </c>
-      <c r="G26" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2344,22 +2548,19 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F27" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2367,22 +2568,22 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G28" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2390,22 +2591,19 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>114</v>
-      </c>
-      <c r="E29" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G29" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2413,22 +2611,16 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" t="s">
-        <v>115</v>
-      </c>
-      <c r="E30" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="F30" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G30" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2436,16 +2628,22 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>120</v>
+      </c>
+      <c r="D31" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" t="s">
+        <v>141</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2453,16 +2651,16 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="F32" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2470,19 +2668,19 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F33" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G33" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2490,19 +2688,19 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="F34" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G34" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2510,19 +2708,19 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>85</v>
+      </c>
+      <c r="E35" t="s">
+        <v>85</v>
       </c>
       <c r="F35" t="s">
-        <v>90</v>
-      </c>
-      <c r="G35" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2530,19 +2728,16 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
-      </c>
-      <c r="D36" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F36" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G36" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2550,16 +2745,19 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
+        <v>125</v>
+      </c>
+      <c r="D37" t="s">
+        <v>77</v>
       </c>
       <c r="F37" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G37" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2567,16 +2765,19 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>68</v>
+      </c>
+      <c r="E38" t="s">
+        <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2584,19 +2785,16 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D39" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G39" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2604,19 +2802,19 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G40" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2624,19 +2822,19 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="D41" t="s">
-        <v>118</v>
+        <v>79</v>
+      </c>
+      <c r="E41" t="s">
+        <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>90</v>
-      </c>
-      <c r="G41" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2644,19 +2842,19 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="C42" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>119</v>
+        <v>79</v>
+      </c>
+      <c r="E42" t="s">
+        <v>79</v>
       </c>
       <c r="F42" t="s">
-        <v>90</v>
-      </c>
-      <c r="G42" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2664,16 +2862,19 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="D43" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" t="s">
+        <v>92</v>
       </c>
       <c r="F43" t="s">
-        <v>91</v>
-      </c>
-      <c r="G43" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2681,16 +2882,19 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>71</v>
+      </c>
+      <c r="D44" t="s">
+        <v>139</v>
+      </c>
+      <c r="E44" t="s">
+        <v>99</v>
       </c>
       <c r="F44" t="s">
-        <v>91</v>
-      </c>
-      <c r="G44" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2698,19 +2902,19 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="D45" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="F45" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G45" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2718,19 +2922,16 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="F46" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G46" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2738,19 +2939,22 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="D47" t="s">
-        <v>68</v>
+        <v>136</v>
+      </c>
+      <c r="E47" t="s">
+        <v>141</v>
       </c>
       <c r="F47" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G47" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2758,19 +2962,16 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="F48" t="s">
-        <v>91</v>
+        <v>103</v>
+      </c>
+      <c r="G48" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2778,19 +2979,19 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
-        <v>76</v>
+        <v>100</v>
+      </c>
+      <c r="E49" t="s">
+        <v>100</v>
       </c>
       <c r="F49" t="s">
-        <v>90</v>
-      </c>
-      <c r="G49" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2798,19 +2999,19 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="D50" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="F50" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G50" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2818,13 +3019,19 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>73</v>
+      </c>
+      <c r="C51" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" t="s">
+        <v>85</v>
       </c>
       <c r="E51" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F51" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2832,13 +3039,16 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
-      </c>
-      <c r="E52" t="s">
-        <v>82</v>
+        <v>131</v>
+      </c>
+      <c r="C52" t="s">
+        <v>131</v>
       </c>
       <c r="F52" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="G52" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2846,13 +3056,19 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
-      </c>
-      <c r="E53" t="s">
-        <v>83</v>
+        <v>132</v>
+      </c>
+      <c r="C53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D53" t="s">
+        <v>77</v>
       </c>
       <c r="F53" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="G53" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2860,13 +3076,16 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
-      </c>
-      <c r="E54" t="s">
-        <v>75</v>
+        <v>133</v>
+      </c>
+      <c r="C54" t="s">
+        <v>133</v>
       </c>
       <c r="F54" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="G54" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2874,13 +3093,16 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
-      </c>
-      <c r="E55" t="s">
-        <v>84</v>
+        <v>51</v>
+      </c>
+      <c r="C55" t="s">
+        <v>51</v>
       </c>
       <c r="F55" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="G55" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2888,13 +3110,19 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
-      </c>
-      <c r="E56" t="s">
-        <v>85</v>
+        <v>52</v>
+      </c>
+      <c r="C56" t="s">
+        <v>52</v>
+      </c>
+      <c r="D56" t="s">
+        <v>77</v>
       </c>
       <c r="F56" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="G56" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2902,13 +3130,19 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
-      </c>
-      <c r="E57" t="s">
-        <v>86</v>
+        <v>53</v>
+      </c>
+      <c r="C57" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" t="s">
+        <v>140</v>
       </c>
       <c r="F57" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="G57" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2916,13 +3150,19 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>59</v>
-      </c>
-      <c r="E58" t="s">
-        <v>75</v>
+        <v>54</v>
+      </c>
+      <c r="C58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" t="s">
+        <v>85</v>
       </c>
       <c r="F58" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="G58" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2930,13 +3170,19 @@
         <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>41</v>
-      </c>
-      <c r="E59" t="s">
-        <v>69</v>
+        <v>55</v>
+      </c>
+      <c r="C59" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" t="s">
+        <v>78</v>
       </c>
       <c r="F59" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="G59" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2944,13 +3190,19 @@
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>42</v>
+        <v>56</v>
+      </c>
+      <c r="C60" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60" t="s">
+        <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="F60" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2958,13 +3210,16 @@
         <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
-      </c>
-      <c r="E61" t="s">
-        <v>79</v>
+        <v>57</v>
+      </c>
+      <c r="C61" t="s">
+        <v>57</v>
       </c>
       <c r="F61" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="G61" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2972,13 +3227,19 @@
         <v>3</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
-      </c>
-      <c r="E62" t="s">
-        <v>75</v>
+        <v>58</v>
+      </c>
+      <c r="C62" t="s">
+        <v>58</v>
+      </c>
+      <c r="D62" t="s">
+        <v>102</v>
       </c>
       <c r="F62" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="G62" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2986,13 +3247,13 @@
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F63" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3000,13 +3261,13 @@
         <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E64" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="F64" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3014,13 +3275,97 @@
         <v>3</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E65" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F65" t="s">
-        <v>92</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" t="s">
+        <v>101</v>
+      </c>
+      <c r="F66" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>75</v>
+      </c>
+      <c r="E67" t="s">
+        <v>85</v>
+      </c>
+      <c r="F67" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>3</v>
+      </c>
+      <c r="B68" t="s">
+        <v>47</v>
+      </c>
+      <c r="E68" t="s">
+        <v>79</v>
+      </c>
+      <c r="F68" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>3</v>
+      </c>
+      <c r="B69" t="s">
+        <v>48</v>
+      </c>
+      <c r="E69" t="s">
+        <v>79</v>
+      </c>
+      <c r="F69" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>3</v>
+      </c>
+      <c r="B70" t="s">
+        <v>49</v>
+      </c>
+      <c r="E70" t="s">
+        <v>93</v>
+      </c>
+      <c r="F70" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>3</v>
+      </c>
+      <c r="B71" t="s">
+        <v>76</v>
+      </c>
+      <c r="E71" t="s">
+        <v>102</v>
+      </c>
+      <c r="F71" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3030,7 +3375,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3067,10 +3412,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3084,13 +3429,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3104,10 +3449,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3121,10 +3466,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3138,13 +3483,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3158,10 +3503,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3174,11 +3519,14 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3192,16 +3540,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3215,16 +3560,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3238,16 +3580,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3255,19 +3594,19 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="G12" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3275,19 +3614,16 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" t="s">
-        <v>151</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3295,19 +3631,19 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="F14" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3315,19 +3651,19 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>79</v>
+      </c>
+      <c r="E15" t="s">
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3335,19 +3671,19 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3355,16 +3691,19 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>37</v>
+      </c>
+      <c r="D17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3372,19 +3711,19 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3392,16 +3731,16 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G19" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3409,19 +3748,19 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G20" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3429,19 +3768,19 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>79</v>
+      </c>
+      <c r="E21" t="s">
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3449,16 +3788,19 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3466,16 +3808,19 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>92</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3483,19 +3828,19 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="G24" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3503,19 +3848,16 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>91</v>
+        <v>103</v>
+      </c>
+      <c r="G25" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3523,19 +3865,19 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
-      </c>
-      <c r="E26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="G26" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3543,19 +3885,19 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3563,19 +3905,19 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>151</v>
+        <v>79</v>
+      </c>
+      <c r="E28" t="s">
+        <v>79</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3583,19 +3925,19 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>157</v>
+        <v>151</v>
+      </c>
+      <c r="E29" t="s">
+        <v>93</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3603,19 +3945,19 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G30" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3623,22 +3965,16 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" t="s">
-        <v>159</v>
-      </c>
-      <c r="E31" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="F31" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G31" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3646,16 +3982,19 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>137</v>
+        <v>145</v>
+      </c>
+      <c r="D32" t="s">
+        <v>77</v>
       </c>
       <c r="F32" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3663,19 +4002,19 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="D33" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F33" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="G33" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3683,16 +4022,19 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C34" t="s">
-        <v>138</v>
+        <v>147</v>
+      </c>
+      <c r="D34" t="s">
+        <v>79</v>
       </c>
       <c r="F34" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G34" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3700,19 +4042,19 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C35" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D35" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="F35" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G35" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3720,19 +4062,19 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" t="s">
-        <v>83</v>
+        <v>149</v>
+      </c>
+      <c r="D36" t="s">
+        <v>81</v>
       </c>
       <c r="F36" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G36" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3740,16 +4082,16 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F37" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G37" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3757,16 +4099,19 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>52</v>
+      </c>
+      <c r="D38" t="s">
+        <v>77</v>
       </c>
       <c r="F38" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3774,19 +4119,19 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D39" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F39" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="G39" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3794,19 +4139,19 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D40" t="s">
-        <v>69</v>
-      </c>
-      <c r="E40" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F40" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="G40" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3814,19 +4159,19 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>160</v>
-      </c>
-      <c r="E41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F41" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="G41" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3834,19 +4179,19 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3854,19 +4199,13 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
-      </c>
-      <c r="C43" t="s">
-        <v>140</v>
-      </c>
-      <c r="D43" t="s">
-        <v>151</v>
+        <v>65</v>
+      </c>
+      <c r="E43" t="s">
+        <v>94</v>
       </c>
       <c r="F43" t="s">
-        <v>90</v>
-      </c>
-      <c r="G43" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3874,19 +4213,13 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" t="s">
-        <v>141</v>
-      </c>
-      <c r="D44" t="s">
-        <v>162</v>
+        <v>66</v>
+      </c>
+      <c r="E44" t="s">
+        <v>95</v>
       </c>
       <c r="F44" t="s">
-        <v>90</v>
-      </c>
-      <c r="G44" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3894,19 +4227,13 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
-      </c>
-      <c r="C45" t="s">
-        <v>142</v>
-      </c>
-      <c r="D45" t="s">
-        <v>163</v>
+        <v>67</v>
+      </c>
+      <c r="E45" t="s">
+        <v>96</v>
       </c>
       <c r="F45" t="s">
-        <v>90</v>
-      </c>
-      <c r="G45" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3914,22 +4241,13 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
-      </c>
-      <c r="C46" t="s">
-        <v>143</v>
-      </c>
-      <c r="D46" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="E46" t="s">
-        <v>165</v>
+        <v>97</v>
       </c>
       <c r="F46" t="s">
-        <v>90</v>
-      </c>
-      <c r="G46" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3937,16 +4255,13 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
-      </c>
-      <c r="C47" t="s">
-        <v>144</v>
+        <v>69</v>
+      </c>
+      <c r="E47" t="s">
+        <v>85</v>
       </c>
       <c r="F47" t="s">
-        <v>91</v>
-      </c>
-      <c r="G47" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3954,372 +4269,97 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" t="s">
+        <v>98</v>
+      </c>
+      <c r="F48" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>3</v>
+      </c>
+      <c r="B49" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" t="s">
+        <v>99</v>
+      </c>
+      <c r="F49" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" t="s">
+        <v>100</v>
+      </c>
+      <c r="F50" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s">
+        <v>73</v>
+      </c>
+      <c r="E51" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>3</v>
+      </c>
+      <c r="B52" t="s">
+        <v>74</v>
+      </c>
+      <c r="E52" t="s">
+        <v>101</v>
+      </c>
+      <c r="F52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53" t="s">
         <v>75</v>
       </c>
-      <c r="E48" t="s">
-        <v>75</v>
-      </c>
-      <c r="F48" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>3</v>
-      </c>
-      <c r="B49" t="s">
-        <v>145</v>
-      </c>
-      <c r="C49" t="s">
-        <v>145</v>
-      </c>
-      <c r="F49" t="s">
-        <v>91</v>
-      </c>
-      <c r="G49" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>3</v>
-      </c>
-      <c r="B50" t="s">
-        <v>146</v>
-      </c>
-      <c r="C50" t="s">
-        <v>146</v>
-      </c>
-      <c r="D50" t="s">
-        <v>111</v>
-      </c>
-      <c r="F50" t="s">
-        <v>90</v>
-      </c>
-      <c r="G50" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>3</v>
-      </c>
-      <c r="B51" t="s">
-        <v>147</v>
-      </c>
-      <c r="C51" t="s">
-        <v>147</v>
-      </c>
-      <c r="F51" t="s">
-        <v>91</v>
-      </c>
-      <c r="G51" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>3</v>
-      </c>
-      <c r="B52" t="s">
-        <v>45</v>
-      </c>
-      <c r="C52" t="s">
-        <v>45</v>
-      </c>
-      <c r="F52" t="s">
-        <v>91</v>
-      </c>
-      <c r="G52" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>3</v>
-      </c>
-      <c r="B53" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" t="s">
-        <v>46</v>
+      <c r="E53" t="s">
+        <v>85</v>
       </c>
       <c r="F53" t="s">
-        <v>91</v>
-      </c>
-      <c r="G53" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>47</v>
-      </c>
-      <c r="C54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D54" t="s">
-        <v>148</v>
+        <v>76</v>
+      </c>
+      <c r="E54" t="s">
+        <v>102</v>
       </c>
       <c r="F54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G54" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>3</v>
-      </c>
-      <c r="B55" t="s">
-        <v>48</v>
-      </c>
-      <c r="C55" t="s">
-        <v>48</v>
-      </c>
-      <c r="D55" t="s">
-        <v>75</v>
-      </c>
-      <c r="F55" t="s">
-        <v>90</v>
-      </c>
-      <c r="G55" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>3</v>
-      </c>
-      <c r="B56" t="s">
-        <v>49</v>
-      </c>
-      <c r="C56" t="s">
-        <v>49</v>
-      </c>
-      <c r="D56" t="s">
-        <v>68</v>
-      </c>
-      <c r="F56" t="s">
-        <v>90</v>
-      </c>
-      <c r="G56" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
-        <v>3</v>
-      </c>
-      <c r="B57" t="s">
-        <v>50</v>
-      </c>
-      <c r="C57" t="s">
-        <v>50</v>
-      </c>
-      <c r="D57" t="s">
-        <v>164</v>
-      </c>
-      <c r="E57" t="s">
-        <v>76</v>
-      </c>
-      <c r="F57" t="s">
-        <v>90</v>
-      </c>
-      <c r="G57" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58">
-        <v>3</v>
-      </c>
-      <c r="B58" t="s">
-        <v>29</v>
-      </c>
-      <c r="E58" t="s">
-        <v>69</v>
-      </c>
-      <c r="F58" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
-        <v>3</v>
-      </c>
-      <c r="B59" t="s">
-        <v>30</v>
-      </c>
-      <c r="E59" t="s">
-        <v>69</v>
-      </c>
-      <c r="F59" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60">
-        <v>3</v>
-      </c>
-      <c r="B60" t="s">
-        <v>31</v>
-      </c>
-      <c r="E60" t="s">
-        <v>77</v>
-      </c>
-      <c r="F60" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61">
-        <v>3</v>
-      </c>
-      <c r="B61" t="s">
-        <v>54</v>
-      </c>
-      <c r="E61" t="s">
-        <v>83</v>
-      </c>
-      <c r="F61" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62">
-        <v>3</v>
-      </c>
-      <c r="B62" t="s">
-        <v>56</v>
-      </c>
-      <c r="E62" t="s">
-        <v>84</v>
-      </c>
-      <c r="F62" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63">
-        <v>3</v>
-      </c>
-      <c r="B63" t="s">
-        <v>58</v>
-      </c>
-      <c r="E63" t="s">
-        <v>86</v>
-      </c>
-      <c r="F63" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64">
-        <v>3</v>
-      </c>
-      <c r="B64" t="s">
-        <v>60</v>
-      </c>
-      <c r="E64" t="s">
-        <v>87</v>
-      </c>
-      <c r="F64" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>3</v>
-      </c>
-      <c r="B65" t="s">
-        <v>61</v>
-      </c>
-      <c r="E65" t="s">
-        <v>75</v>
-      </c>
-      <c r="F65" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>3</v>
-      </c>
-      <c r="B66" t="s">
-        <v>62</v>
-      </c>
-      <c r="E66" t="s">
-        <v>69</v>
-      </c>
-      <c r="F66" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>3</v>
-      </c>
-      <c r="B67" t="s">
-        <v>63</v>
-      </c>
-      <c r="E67" t="s">
-        <v>69</v>
-      </c>
-      <c r="F67" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>3</v>
-      </c>
-      <c r="B68" t="s">
-        <v>64</v>
-      </c>
-      <c r="E68" t="s">
-        <v>88</v>
-      </c>
-      <c r="F68" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>3</v>
-      </c>
-      <c r="B69" t="s">
-        <v>65</v>
-      </c>
-      <c r="E69" t="s">
-        <v>89</v>
-      </c>
-      <c r="F69" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>3</v>
-      </c>
-      <c r="B70" t="s">
-        <v>50</v>
-      </c>
-      <c r="E70" t="s">
-        <v>76</v>
-      </c>
-      <c r="F70" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -4329,7 +4369,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -4371,14 +4411,11 @@
       <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
-        <v>66</v>
-      </c>
       <c r="G2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4395,13 +4432,13 @@
         <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H3" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4418,10 +4455,10 @@
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H4" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4438,10 +4475,10 @@
         <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H5" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4458,13 +4495,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H6" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4481,10 +4518,10 @@
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H7" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4500,11 +4537,14 @@
       <c r="D8" t="s">
         <v>28</v>
       </c>
+      <c r="E8" t="s">
+        <v>77</v>
+      </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H8" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4521,13 +4561,13 @@
         <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4544,13 +4584,13 @@
         <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4567,13 +4607,13 @@
         <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4590,13 +4630,13 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H12" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -4613,10 +4653,10 @@
         <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H13" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4632,11 +4672,14 @@
       <c r="D14" t="s">
         <v>34</v>
       </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
       <c r="G14" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H14" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4653,13 +4696,13 @@
         <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4676,13 +4719,13 @@
         <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4699,13 +4742,13 @@
         <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -4722,13 +4765,13 @@
         <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H18" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -4745,10 +4788,10 @@
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H19" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -4764,11 +4807,14 @@
       <c r="D20" t="s">
         <v>40</v>
       </c>
+      <c r="E20" t="s">
+        <v>77</v>
+      </c>
       <c r="G20" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H20" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -4785,13 +4831,13 @@
         <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -4808,13 +4854,13 @@
         <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4831,13 +4877,13 @@
         <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G23" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -4854,13 +4900,13 @@
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H24" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4877,10 +4923,10 @@
         <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H25" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4896,11 +4942,14 @@
       <c r="D26" t="s">
         <v>46</v>
       </c>
+      <c r="E26" t="s">
+        <v>77</v>
+      </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H26" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4917,13 +4966,13 @@
         <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>79</v>
+      </c>
+      <c r="F27" t="s">
+        <v>79</v>
       </c>
       <c r="G27" t="s">
-        <v>90</v>
-      </c>
-      <c r="H27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4940,13 +4989,13 @@
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>79</v>
+      </c>
+      <c r="F28" t="s">
+        <v>79</v>
       </c>
       <c r="G28" t="s">
-        <v>90</v>
-      </c>
-      <c r="H28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4963,13 +5012,16 @@
         <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>68</v>
+        <v>84</v>
+      </c>
+      <c r="F29" t="s">
+        <v>93</v>
       </c>
       <c r="G29" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H29" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4986,13 +5038,13 @@
         <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="H30" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5005,11 +5057,14 @@
       <c r="C31" t="s">
         <v>51</v>
       </c>
-      <c r="F31" t="s">
-        <v>80</v>
+      <c r="D31" t="s">
+        <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="H31" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5022,11 +5077,17 @@
       <c r="C32" t="s">
         <v>52</v>
       </c>
-      <c r="F32" t="s">
-        <v>81</v>
+      <c r="D32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" t="s">
+        <v>77</v>
       </c>
       <c r="G32" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H32" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -5039,11 +5100,17 @@
       <c r="C33" t="s">
         <v>53</v>
       </c>
-      <c r="F33" t="s">
-        <v>82</v>
+      <c r="D33" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33" t="s">
+        <v>79</v>
       </c>
       <c r="G33" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H33" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -5056,11 +5123,17 @@
       <c r="C34" t="s">
         <v>54</v>
       </c>
-      <c r="F34" t="s">
-        <v>83</v>
+      <c r="D34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" t="s">
+        <v>85</v>
       </c>
       <c r="G34" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H34" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -5073,11 +5146,17 @@
       <c r="C35" t="s">
         <v>55</v>
       </c>
-      <c r="F35" t="s">
-        <v>75</v>
+      <c r="D35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" t="s">
+        <v>78</v>
       </c>
       <c r="G35" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H35" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -5090,11 +5169,17 @@
       <c r="C36" t="s">
         <v>56</v>
       </c>
+      <c r="D36" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" t="s">
+        <v>86</v>
+      </c>
       <c r="F36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G36" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -5107,11 +5192,17 @@
       <c r="C37" t="s">
         <v>57</v>
       </c>
-      <c r="F37" t="s">
-        <v>85</v>
+      <c r="D37" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" t="s">
+        <v>86</v>
       </c>
       <c r="G37" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H37" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -5124,11 +5215,17 @@
       <c r="C38" t="s">
         <v>58</v>
       </c>
-      <c r="F38" t="s">
-        <v>86</v>
+      <c r="D38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" t="s">
+        <v>87</v>
       </c>
       <c r="G38" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H38" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -5141,11 +5238,14 @@
       <c r="C39" t="s">
         <v>59</v>
       </c>
-      <c r="F39" t="s">
-        <v>75</v>
+      <c r="D39" t="s">
+        <v>59</v>
       </c>
       <c r="G39" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="H39" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -5158,11 +5258,17 @@
       <c r="C40" t="s">
         <v>60</v>
       </c>
-      <c r="F40" t="s">
-        <v>87</v>
+      <c r="D40" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" t="s">
+        <v>77</v>
       </c>
       <c r="G40" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H40" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -5175,11 +5281,17 @@
       <c r="C41" t="s">
         <v>61</v>
       </c>
-      <c r="F41" t="s">
-        <v>75</v>
+      <c r="D41" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" t="s">
+        <v>88</v>
       </c>
       <c r="G41" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H41" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -5192,11 +5304,14 @@
       <c r="C42" t="s">
         <v>62</v>
       </c>
-      <c r="F42" t="s">
-        <v>69</v>
+      <c r="D42" t="s">
+        <v>62</v>
       </c>
       <c r="G42" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="H42" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -5209,11 +5324,17 @@
       <c r="C43" t="s">
         <v>63</v>
       </c>
-      <c r="F43" t="s">
-        <v>69</v>
+      <c r="D43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" t="s">
+        <v>89</v>
       </c>
       <c r="G43" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H43" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -5226,11 +5347,17 @@
       <c r="C44" t="s">
         <v>64</v>
       </c>
-      <c r="F44" t="s">
-        <v>88</v>
+      <c r="D44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" t="s">
+        <v>77</v>
       </c>
       <c r="G44" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H44" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -5244,10 +5371,10 @@
         <v>65</v>
       </c>
       <c r="F45" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G45" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -5255,19 +5382,16 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" t="s">
-        <v>22</v>
+        <v>66</v>
+      </c>
+      <c r="F46" t="s">
+        <v>95</v>
       </c>
       <c r="G46" t="s">
-        <v>91</v>
-      </c>
-      <c r="H46" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -5275,22 +5399,16 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
-      </c>
-      <c r="D47" t="s">
-        <v>23</v>
-      </c>
-      <c r="E47" t="s">
-        <v>111</v>
+        <v>67</v>
+      </c>
+      <c r="F47" t="s">
+        <v>96</v>
       </c>
       <c r="G47" t="s">
-        <v>90</v>
-      </c>
-      <c r="H47" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -5298,19 +5416,16 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" t="s">
-        <v>24</v>
+        <v>68</v>
+      </c>
+      <c r="F48" t="s">
+        <v>97</v>
       </c>
       <c r="G48" t="s">
-        <v>91</v>
-      </c>
-      <c r="H48" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -5318,19 +5433,16 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
-      </c>
-      <c r="D49" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="F49" t="s">
+        <v>85</v>
       </c>
       <c r="G49" t="s">
-        <v>91</v>
-      </c>
-      <c r="H49" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -5338,22 +5450,16 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
-      </c>
-      <c r="D50" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="F50" t="s">
+        <v>98</v>
       </c>
       <c r="G50" t="s">
-        <v>90</v>
-      </c>
-      <c r="H50" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -5361,19 +5467,16 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D51" t="s">
-        <v>27</v>
+        <v>71</v>
+      </c>
+      <c r="F51" t="s">
+        <v>99</v>
       </c>
       <c r="G51" t="s">
-        <v>91</v>
-      </c>
-      <c r="H51" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -5381,19 +5484,16 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>28</v>
-      </c>
-      <c r="D52" t="s">
-        <v>28</v>
+        <v>72</v>
+      </c>
+      <c r="F52" t="s">
+        <v>100</v>
       </c>
       <c r="G52" t="s">
-        <v>91</v>
-      </c>
-      <c r="H52" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -5401,22 +5501,16 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
-      </c>
-      <c r="D53" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F53" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="G53" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -5424,22 +5518,16 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
-      </c>
-      <c r="D54" t="s">
-        <v>30</v>
-      </c>
-      <c r="E54" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F54" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="G54" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -5447,22 +5535,16 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
-      </c>
-      <c r="D55" t="s">
-        <v>31</v>
-      </c>
-      <c r="E55" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F55" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G55" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -5470,22 +5552,16 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>51</v>
-      </c>
-      <c r="D56" t="s">
-        <v>51</v>
-      </c>
-      <c r="E56" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="F56" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -5493,19 +5569,16 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
-      </c>
-      <c r="D57" t="s">
-        <v>33</v>
+        <v>76</v>
+      </c>
+      <c r="F57" t="s">
+        <v>102</v>
       </c>
       <c r="G57" t="s">
-        <v>91</v>
-      </c>
-      <c r="H57" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -5516,16 +5589,16 @@
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D58" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G58" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H58" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -5536,19 +5609,19 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D59" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E59" t="s">
-        <v>69</v>
-      </c>
-      <c r="F59" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G59" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="H59" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -5559,19 +5632,16 @@
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
-      </c>
-      <c r="E60" t="s">
-        <v>69</v>
-      </c>
-      <c r="F60" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="G60" t="s">
-        <v>91</v>
+        <v>103</v>
+      </c>
+      <c r="H60" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -5582,19 +5652,16 @@
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>37</v>
-      </c>
-      <c r="E61" t="s">
-        <v>78</v>
-      </c>
-      <c r="F61" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="G61" t="s">
-        <v>91</v>
+        <v>103</v>
+      </c>
+      <c r="H61" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -5605,22 +5672,19 @@
         <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D62" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>113</v>
-      </c>
-      <c r="F62" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H62" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -5631,16 +5695,16 @@
         <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G63" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H63" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -5651,16 +5715,19 @@
         <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="D64" t="s">
-        <v>40</v>
+        <v>28</v>
+      </c>
+      <c r="E64" t="s">
+        <v>77</v>
       </c>
       <c r="G64" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H64" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -5671,22 +5738,19 @@
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="D65" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E65" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F65" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s">
-        <v>90</v>
-      </c>
-      <c r="H65" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -5697,22 +5761,19 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D66" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E66" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F66" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s">
-        <v>90</v>
-      </c>
-      <c r="H66" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -5723,19 +5784,19 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D67" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E67" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F67" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -5746,19 +5807,19 @@
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D68" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E68" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="F68" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G68" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -5769,16 +5830,19 @@
         <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="D69" t="s">
-        <v>95</v>
+        <v>109</v>
+      </c>
+      <c r="E69" t="s">
+        <v>135</v>
       </c>
       <c r="G69" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H69" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -5789,16 +5853,16 @@
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="D70" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="G70" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H70" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -5809,22 +5873,19 @@
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E71" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="F71" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="G71" t="s">
-        <v>90</v>
-      </c>
-      <c r="H71" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -5835,22 +5896,16 @@
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
-      </c>
-      <c r="E72" t="s">
-        <v>74</v>
-      </c>
-      <c r="F72" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="G72" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H72" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -5861,22 +5916,19 @@
         <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="D73" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="E73" t="s">
-        <v>114</v>
-      </c>
-      <c r="F73" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="G73" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H73" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -5887,22 +5939,19 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="D74" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="E74" t="s">
-        <v>115</v>
-      </c>
-      <c r="F74" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="G74" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H74" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -5913,16 +5962,19 @@
         <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>97</v>
+        <v>114</v>
+      </c>
+      <c r="E75" t="s">
+        <v>85</v>
       </c>
       <c r="G75" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H75" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -5933,16 +5985,16 @@
         <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D76" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H76" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -5953,19 +6005,19 @@
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D77" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E77" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G77" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H77" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -5976,19 +6028,19 @@
         <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="D78" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="E78" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="G78" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H78" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -5999,19 +6051,16 @@
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="D79" t="s">
-        <v>101</v>
-      </c>
-      <c r="E79" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="G79" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H79" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -6022,19 +6071,19 @@
         <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="D80" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="E80" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="G80" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H80" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -6045,16 +6094,19 @@
         <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="D81" t="s">
-        <v>103</v>
+        <v>35</v>
+      </c>
+      <c r="E81" t="s">
+        <v>79</v>
+      </c>
+      <c r="F81" t="s">
+        <v>79</v>
       </c>
       <c r="G81" t="s">
-        <v>91</v>
-      </c>
-      <c r="H81" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -6065,16 +6117,19 @@
         <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="D82" t="s">
-        <v>104</v>
+        <v>36</v>
+      </c>
+      <c r="E82" t="s">
+        <v>79</v>
+      </c>
+      <c r="F82" t="s">
+        <v>79</v>
       </c>
       <c r="G82" t="s">
-        <v>91</v>
-      </c>
-      <c r="H82" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -6085,19 +6140,19 @@
         <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="D83" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="E83" t="s">
-        <v>74</v>
+        <v>91</v>
+      </c>
+      <c r="F83" t="s">
+        <v>91</v>
       </c>
       <c r="G83" t="s">
-        <v>90</v>
-      </c>
-      <c r="H83" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -6108,19 +6163,22 @@
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="D84" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="E84" t="s">
-        <v>74</v>
+        <v>138</v>
+      </c>
+      <c r="F84" t="s">
+        <v>96</v>
       </c>
       <c r="G84" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H84" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -6131,19 +6189,19 @@
         <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D85" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E85" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="G85" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H85" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -6154,19 +6212,16 @@
         <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="D86" t="s">
-        <v>108</v>
-      </c>
-      <c r="E86" t="s">
         <v>119</v>
       </c>
       <c r="G86" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H86" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -6177,16 +6232,22 @@
         <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="D87" t="s">
-        <v>45</v>
+        <v>120</v>
+      </c>
+      <c r="E87" t="s">
+        <v>136</v>
+      </c>
+      <c r="F87" t="s">
+        <v>141</v>
       </c>
       <c r="G87" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H87" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -6197,16 +6258,16 @@
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="D88" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="G88" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H88" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -6217,19 +6278,19 @@
         <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="D89" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="E89" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G89" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H89" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -6240,19 +6301,19 @@
         <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="D90" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="E90" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="G90" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H90" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -6263,19 +6324,19 @@
         <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D91" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E91" t="s">
-        <v>68</v>
+        <v>85</v>
+      </c>
+      <c r="F91" t="s">
+        <v>85</v>
       </c>
       <c r="G91" t="s">
-        <v>90</v>
-      </c>
-      <c r="H91" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -6286,19 +6347,16 @@
         <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>50</v>
-      </c>
-      <c r="E92" t="s">
-        <v>76</v>
-      </c>
-      <c r="F92" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="G92" t="s">
-        <v>91</v>
+        <v>103</v>
+      </c>
+      <c r="H92" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -6309,19 +6367,19 @@
         <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D93" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E93" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G93" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H93" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -6332,19 +6390,19 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="D94" t="s">
-        <v>110</v>
-      </c>
-      <c r="E94" t="s">
-        <v>120</v>
+        <v>68</v>
+      </c>
+      <c r="F94" t="s">
+        <v>97</v>
       </c>
       <c r="G94" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H94" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -6355,13 +6413,16 @@
         <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>52</v>
-      </c>
-      <c r="F95" t="s">
-        <v>81</v>
+        <v>39</v>
+      </c>
+      <c r="D95" t="s">
+        <v>39</v>
       </c>
       <c r="G95" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="H95" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -6372,13 +6433,19 @@
         <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>53</v>
-      </c>
-      <c r="F96" t="s">
-        <v>82</v>
+        <v>40</v>
+      </c>
+      <c r="D96" t="s">
+        <v>40</v>
+      </c>
+      <c r="E96" t="s">
+        <v>77</v>
       </c>
       <c r="G96" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H96" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -6389,13 +6456,19 @@
         <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>54</v>
+        <v>41</v>
+      </c>
+      <c r="D97" t="s">
+        <v>41</v>
+      </c>
+      <c r="E97" t="s">
+        <v>79</v>
       </c>
       <c r="F97" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G97" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -6406,13 +6479,19 @@
         <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>55</v>
+        <v>42</v>
+      </c>
+      <c r="D98" t="s">
+        <v>42</v>
+      </c>
+      <c r="E98" t="s">
+        <v>79</v>
       </c>
       <c r="F98" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G98" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -6423,13 +6502,19 @@
         <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>56</v>
+        <v>43</v>
+      </c>
+      <c r="D99" t="s">
+        <v>43</v>
+      </c>
+      <c r="E99" t="s">
+        <v>92</v>
       </c>
       <c r="F99" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G99" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -6440,13 +6525,19 @@
         <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>57</v>
+        <v>71</v>
+      </c>
+      <c r="D100" t="s">
+        <v>71</v>
+      </c>
+      <c r="E100" t="s">
+        <v>139</v>
       </c>
       <c r="F100" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="G100" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -6457,13 +6548,19 @@
         <v>13</v>
       </c>
       <c r="C101" t="s">
-        <v>58</v>
-      </c>
-      <c r="F101" t="s">
-        <v>86</v>
+        <v>126</v>
+      </c>
+      <c r="D101" t="s">
+        <v>126</v>
+      </c>
+      <c r="E101" t="s">
+        <v>135</v>
       </c>
       <c r="G101" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H101" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -6474,13 +6571,16 @@
         <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>59</v>
-      </c>
-      <c r="F102" t="s">
-        <v>75</v>
+        <v>127</v>
+      </c>
+      <c r="D102" t="s">
+        <v>127</v>
       </c>
       <c r="G102" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="H102" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -6491,13 +6591,22 @@
         <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>41</v>
+        <v>128</v>
+      </c>
+      <c r="D103" t="s">
+        <v>128</v>
+      </c>
+      <c r="E103" t="s">
+        <v>136</v>
       </c>
       <c r="F103" t="s">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="G103" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H103" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -6508,13 +6617,16 @@
         <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>42</v>
-      </c>
-      <c r="F104" t="s">
-        <v>69</v>
+        <v>129</v>
+      </c>
+      <c r="D104" t="s">
+        <v>129</v>
       </c>
       <c r="G104" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="H104" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -6525,13 +6637,19 @@
         <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>43</v>
+        <v>72</v>
+      </c>
+      <c r="D105" t="s">
+        <v>72</v>
+      </c>
+      <c r="E105" t="s">
+        <v>100</v>
       </c>
       <c r="F105" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="G105" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -6542,13 +6660,19 @@
         <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>61</v>
-      </c>
-      <c r="F106" t="s">
-        <v>75</v>
+        <v>130</v>
+      </c>
+      <c r="D106" t="s">
+        <v>130</v>
+      </c>
+      <c r="E106" t="s">
+        <v>137</v>
       </c>
       <c r="G106" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H106" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -6559,13 +6683,19 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>62</v>
+        <v>73</v>
+      </c>
+      <c r="D107" t="s">
+        <v>73</v>
+      </c>
+      <c r="E107" t="s">
+        <v>85</v>
       </c>
       <c r="F107" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="G107" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -6576,13 +6706,16 @@
         <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>63</v>
-      </c>
-      <c r="F108" t="s">
-        <v>69</v>
+        <v>131</v>
+      </c>
+      <c r="D108" t="s">
+        <v>131</v>
       </c>
       <c r="G108" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="H108" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -6593,13 +6726,19 @@
         <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>65</v>
-      </c>
-      <c r="F109" t="s">
-        <v>89</v>
+        <v>132</v>
+      </c>
+      <c r="D109" t="s">
+        <v>132</v>
+      </c>
+      <c r="E109" t="s">
+        <v>77</v>
       </c>
       <c r="G109" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H109" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -6607,19 +6746,19 @@
         <v>3</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="D110" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="G110" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H110" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -6627,22 +6766,19 @@
         <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D111" t="s">
-        <v>23</v>
-      </c>
-      <c r="E111" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="G111" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H111" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -6650,19 +6786,22 @@
         <v>3</v>
       </c>
       <c r="B112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D112" t="s">
-        <v>24</v>
+        <v>52</v>
+      </c>
+      <c r="E112" t="s">
+        <v>77</v>
       </c>
       <c r="G112" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H112" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -6670,19 +6809,22 @@
         <v>3</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D113" t="s">
-        <v>25</v>
+        <v>53</v>
+      </c>
+      <c r="E113" t="s">
+        <v>140</v>
       </c>
       <c r="G113" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H113" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6690,22 +6832,22 @@
         <v>3</v>
       </c>
       <c r="B114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="D114" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="E114" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G114" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H114" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -6713,19 +6855,22 @@
         <v>3</v>
       </c>
       <c r="B115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="D115" t="s">
-        <v>27</v>
+        <v>55</v>
+      </c>
+      <c r="E115" t="s">
+        <v>78</v>
       </c>
       <c r="G115" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H115" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -6733,19 +6878,22 @@
         <v>3</v>
       </c>
       <c r="B116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="D116" t="s">
-        <v>28</v>
+        <v>56</v>
+      </c>
+      <c r="E116" t="s">
+        <v>86</v>
+      </c>
+      <c r="F116" t="s">
+        <v>86</v>
       </c>
       <c r="G116" t="s">
-        <v>91</v>
-      </c>
-      <c r="H116" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -6753,25 +6901,19 @@
         <v>3</v>
       </c>
       <c r="B117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D117" t="s">
-        <v>29</v>
-      </c>
-      <c r="E117" t="s">
-        <v>148</v>
-      </c>
-      <c r="F117" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G117" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H117" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -6779,25 +6921,22 @@
         <v>3</v>
       </c>
       <c r="B118" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D118" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="E118" t="s">
-        <v>148</v>
-      </c>
-      <c r="F118" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="G118" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H118" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -6805,25 +6944,16 @@
         <v>3</v>
       </c>
       <c r="B119" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C119" t="s">
-        <v>31</v>
-      </c>
-      <c r="D119" t="s">
-        <v>31</v>
-      </c>
-      <c r="E119" t="s">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="F119" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="G119" t="s">
-        <v>90</v>
-      </c>
-      <c r="H119" t="s">
-        <v>166</v>
+        <v>105</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -6831,22 +6961,16 @@
         <v>3</v>
       </c>
       <c r="B120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>51</v>
-      </c>
-      <c r="D120" t="s">
-        <v>51</v>
-      </c>
-      <c r="E120" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="F120" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="G120" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -6854,22 +6978,16 @@
         <v>3</v>
       </c>
       <c r="B121" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>125</v>
-      </c>
-      <c r="D121" t="s">
-        <v>125</v>
-      </c>
-      <c r="E121" t="s">
-        <v>151</v>
+        <v>70</v>
+      </c>
+      <c r="F121" t="s">
+        <v>98</v>
       </c>
       <c r="G121" t="s">
-        <v>90</v>
-      </c>
-      <c r="H121" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -6877,22 +6995,16 @@
         <v>3</v>
       </c>
       <c r="B122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>126</v>
-      </c>
-      <c r="D122" t="s">
-        <v>126</v>
-      </c>
-      <c r="E122" t="s">
-        <v>152</v>
+        <v>74</v>
+      </c>
+      <c r="F122" t="s">
+        <v>101</v>
       </c>
       <c r="G122" t="s">
-        <v>90</v>
-      </c>
-      <c r="H122" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -6900,22 +7012,16 @@
         <v>3</v>
       </c>
       <c r="B123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>127</v>
-      </c>
-      <c r="D123" t="s">
-        <v>127</v>
-      </c>
-      <c r="E123" t="s">
-        <v>153</v>
+        <v>75</v>
+      </c>
+      <c r="F123" t="s">
+        <v>85</v>
       </c>
       <c r="G123" t="s">
-        <v>90</v>
-      </c>
-      <c r="H123" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -6923,22 +7029,16 @@
         <v>3</v>
       </c>
       <c r="B124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>52</v>
-      </c>
-      <c r="D124" t="s">
-        <v>52</v>
-      </c>
-      <c r="E124" t="s">
-        <v>154</v>
+        <v>47</v>
       </c>
       <c r="F124" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G124" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -6946,19 +7046,16 @@
         <v>3</v>
       </c>
       <c r="B125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>128</v>
-      </c>
-      <c r="D125" t="s">
-        <v>128</v>
+        <v>48</v>
+      </c>
+      <c r="F125" t="s">
+        <v>79</v>
       </c>
       <c r="G125" t="s">
-        <v>91</v>
-      </c>
-      <c r="H125" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -6966,22 +7063,16 @@
         <v>3</v>
       </c>
       <c r="B126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>129</v>
-      </c>
-      <c r="D126" t="s">
-        <v>129</v>
-      </c>
-      <c r="E126" t="s">
-        <v>75</v>
+        <v>49</v>
+      </c>
+      <c r="F126" t="s">
+        <v>93</v>
       </c>
       <c r="G126" t="s">
-        <v>90</v>
-      </c>
-      <c r="H126" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -6989,19 +7080,16 @@
         <v>3</v>
       </c>
       <c r="B127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>130</v>
-      </c>
-      <c r="D127" t="s">
-        <v>130</v>
+        <v>76</v>
+      </c>
+      <c r="F127" t="s">
+        <v>102</v>
       </c>
       <c r="G127" t="s">
-        <v>91</v>
-      </c>
-      <c r="H127" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -7012,19 +7100,16 @@
         <v>14</v>
       </c>
       <c r="C128" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="D128" t="s">
-        <v>131</v>
-      </c>
-      <c r="E128" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="G128" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H128" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -7035,19 +7120,19 @@
         <v>14</v>
       </c>
       <c r="C129" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="E129" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G129" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H129" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -7058,16 +7143,16 @@
         <v>14</v>
       </c>
       <c r="C130" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D130" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G130" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H130" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -7078,16 +7163,16 @@
         <v>14</v>
       </c>
       <c r="C131" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G131" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H131" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -7098,19 +7183,19 @@
         <v>14</v>
       </c>
       <c r="C132" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D132" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E132" t="s">
-        <v>69</v>
-      </c>
-      <c r="F132" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G132" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="H132" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -7121,19 +7206,16 @@
         <v>14</v>
       </c>
       <c r="C133" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D133" t="s">
-        <v>36</v>
-      </c>
-      <c r="E133" t="s">
-        <v>69</v>
-      </c>
-      <c r="F133" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="G133" t="s">
-        <v>91</v>
+        <v>103</v>
+      </c>
+      <c r="H133" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -7144,19 +7226,19 @@
         <v>14</v>
       </c>
       <c r="C134" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D134" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E134" t="s">
-        <v>155</v>
-      </c>
-      <c r="F134" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G134" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="H134" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -7167,19 +7249,19 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D135" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E135" t="s">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="F135" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G135" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -7190,19 +7272,19 @@
         <v>14</v>
       </c>
       <c r="C136" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="D136" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="E136" t="s">
-        <v>151</v>
+        <v>79</v>
+      </c>
+      <c r="F136" t="s">
+        <v>79</v>
       </c>
       <c r="G136" t="s">
-        <v>90</v>
-      </c>
-      <c r="H136" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -7213,19 +7295,19 @@
         <v>14</v>
       </c>
       <c r="C137" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="D137" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="E137" t="s">
-        <v>157</v>
+        <v>150</v>
+      </c>
+      <c r="F137" t="s">
+        <v>90</v>
       </c>
       <c r="G137" t="s">
-        <v>90</v>
-      </c>
-      <c r="H137" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -7236,19 +7318,19 @@
         <v>14</v>
       </c>
       <c r="C138" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="D138" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="E138" t="s">
-        <v>158</v>
+        <v>81</v>
       </c>
       <c r="G138" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H138" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -7259,22 +7341,16 @@
         <v>14</v>
       </c>
       <c r="C139" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="D139" t="s">
-        <v>136</v>
-      </c>
-      <c r="E139" t="s">
-        <v>159</v>
-      </c>
-      <c r="F139" t="s">
-        <v>165</v>
+        <v>33</v>
       </c>
       <c r="G139" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H139" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -7285,16 +7361,19 @@
         <v>14</v>
       </c>
       <c r="C140" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="D140" t="s">
-        <v>137</v>
+        <v>34</v>
+      </c>
+      <c r="E140" t="s">
+        <v>77</v>
       </c>
       <c r="G140" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H140" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -7305,19 +7384,19 @@
         <v>14</v>
       </c>
       <c r="C141" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="D141" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="E141" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F141" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G141" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -7328,16 +7407,19 @@
         <v>14</v>
       </c>
       <c r="C142" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s">
-        <v>138</v>
+        <v>36</v>
+      </c>
+      <c r="E142" t="s">
+        <v>79</v>
+      </c>
+      <c r="F142" t="s">
+        <v>79</v>
       </c>
       <c r="G142" t="s">
-        <v>91</v>
-      </c>
-      <c r="H142" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -7348,19 +7430,19 @@
         <v>14</v>
       </c>
       <c r="C143" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="D143" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>111</v>
+        <v>82</v>
+      </c>
+      <c r="F143" t="s">
+        <v>91</v>
       </c>
       <c r="G143" t="s">
-        <v>90</v>
-      </c>
-      <c r="H143" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -7371,19 +7453,19 @@
         <v>14</v>
       </c>
       <c r="C144" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D144" t="s">
-        <v>54</v>
-      </c>
-      <c r="F144" t="s">
-        <v>83</v>
+        <v>38</v>
+      </c>
+      <c r="E144" t="s">
+        <v>81</v>
       </c>
       <c r="G144" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H144" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -7400,10 +7482,10 @@
         <v>39</v>
       </c>
       <c r="G145" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H145" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -7419,11 +7501,14 @@
       <c r="D146" t="s">
         <v>40</v>
       </c>
+      <c r="E146" t="s">
+        <v>77</v>
+      </c>
       <c r="G146" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H146" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -7440,13 +7525,13 @@
         <v>41</v>
       </c>
       <c r="E147" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F147" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G147" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -7463,13 +7548,13 @@
         <v>42</v>
       </c>
       <c r="E148" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F148" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G148" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -7486,13 +7571,13 @@
         <v>43</v>
       </c>
       <c r="E149" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="F149" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G149" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -7503,19 +7588,19 @@
         <v>14</v>
       </c>
       <c r="C150" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D150" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E150" t="s">
-        <v>161</v>
-      </c>
-      <c r="F150" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G150" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="H150" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -7526,19 +7611,16 @@
         <v>14</v>
       </c>
       <c r="C151" t="s">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="D151" t="s">
-        <v>140</v>
-      </c>
-      <c r="E151" t="s">
-        <v>151</v>
+        <v>45</v>
       </c>
       <c r="G151" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H151" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -7549,19 +7631,19 @@
         <v>14</v>
       </c>
       <c r="C152" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="D152" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="E152" t="s">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="G152" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H152" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -7572,19 +7654,19 @@
         <v>14</v>
       </c>
       <c r="C153" t="s">
-        <v>142</v>
+        <v>47</v>
       </c>
       <c r="D153" t="s">
-        <v>142</v>
+        <v>47</v>
       </c>
       <c r="E153" t="s">
-        <v>163</v>
+        <v>79</v>
+      </c>
+      <c r="F153" t="s">
+        <v>79</v>
       </c>
       <c r="G153" t="s">
-        <v>90</v>
-      </c>
-      <c r="H153" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -7595,22 +7677,19 @@
         <v>14</v>
       </c>
       <c r="C154" t="s">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="D154" t="s">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="E154" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="F154" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="G154" t="s">
-        <v>90</v>
-      </c>
-      <c r="H154" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -7621,16 +7700,19 @@
         <v>14</v>
       </c>
       <c r="C155" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>144</v>
+        <v>49</v>
+      </c>
+      <c r="E155" t="s">
+        <v>151</v>
+      </c>
+      <c r="F155" t="s">
+        <v>93</v>
       </c>
       <c r="G155" t="s">
-        <v>91</v>
-      </c>
-      <c r="H155" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -7641,19 +7723,19 @@
         <v>14</v>
       </c>
       <c r="C156" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D156" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E156" t="s">
-        <v>75</v>
-      </c>
-      <c r="F156" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G156" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="H156" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -7664,16 +7746,16 @@
         <v>14</v>
       </c>
       <c r="C157" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D157" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G157" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H157" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -7684,19 +7766,19 @@
         <v>14</v>
       </c>
       <c r="C158" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D158" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E158" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="G158" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H158" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -7707,16 +7789,19 @@
         <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D159" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+      <c r="E159" t="s">
+        <v>79</v>
       </c>
       <c r="G159" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H159" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -7727,16 +7812,19 @@
         <v>14</v>
       </c>
       <c r="C160" t="s">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="D160" t="s">
-        <v>45</v>
+        <v>147</v>
+      </c>
+      <c r="E160" t="s">
+        <v>79</v>
       </c>
       <c r="G160" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H160" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -7747,16 +7835,19 @@
         <v>14</v>
       </c>
       <c r="C161" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="D161" t="s">
-        <v>46</v>
+        <v>148</v>
+      </c>
+      <c r="E161" t="s">
+        <v>84</v>
       </c>
       <c r="G161" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H161" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -7767,19 +7858,19 @@
         <v>14</v>
       </c>
       <c r="C162" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="D162" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="E162" t="s">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="G162" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H162" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -7790,19 +7881,16 @@
         <v>14</v>
       </c>
       <c r="C163" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D163" t="s">
-        <v>48</v>
-      </c>
-      <c r="E163" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="G163" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H163" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -7813,19 +7901,19 @@
         <v>14</v>
       </c>
       <c r="C164" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D164" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E164" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G164" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H164" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -7836,22 +7924,19 @@
         <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D165" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E165" t="s">
-        <v>164</v>
-      </c>
-      <c r="F165" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G165" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H165" t="s">
-        <v>168</v>
+        <v>107</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -7862,13 +7947,19 @@
         <v>14</v>
       </c>
       <c r="C166" t="s">
-        <v>29</v>
-      </c>
-      <c r="F166" t="s">
-        <v>69</v>
+        <v>54</v>
+      </c>
+      <c r="D166" t="s">
+        <v>54</v>
+      </c>
+      <c r="E166" t="s">
+        <v>85</v>
       </c>
       <c r="G166" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H166" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -7879,13 +7970,19 @@
         <v>14</v>
       </c>
       <c r="C167" t="s">
-        <v>30</v>
-      </c>
-      <c r="F167" t="s">
-        <v>69</v>
+        <v>55</v>
+      </c>
+      <c r="D167" t="s">
+        <v>55</v>
+      </c>
+      <c r="E167" t="s">
+        <v>78</v>
       </c>
       <c r="G167" t="s">
-        <v>92</v>
+        <v>104</v>
+      </c>
+      <c r="H167" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -7896,13 +7993,19 @@
         <v>14</v>
       </c>
       <c r="C168" t="s">
-        <v>31</v>
+        <v>56</v>
+      </c>
+      <c r="D168" t="s">
+        <v>56</v>
+      </c>
+      <c r="E168" t="s">
+        <v>86</v>
       </c>
       <c r="F168" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G168" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -7913,13 +8016,13 @@
         <v>14</v>
       </c>
       <c r="C169" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F169" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G169" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -7930,13 +8033,13 @@
         <v>14</v>
       </c>
       <c r="C170" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F170" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G170" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -7947,13 +8050,13 @@
         <v>14</v>
       </c>
       <c r="C171" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F171" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G171" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -7964,13 +8067,13 @@
         <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F172" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G172" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -7981,13 +8084,13 @@
         <v>14</v>
       </c>
       <c r="C173" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F173" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G173" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -7998,13 +8101,13 @@
         <v>14</v>
       </c>
       <c r="C174" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F174" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="G174" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -8015,13 +8118,13 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F175" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G175" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -8032,13 +8135,13 @@
         <v>14</v>
       </c>
       <c r="C176" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F176" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G176" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -8049,13 +8152,13 @@
         <v>14</v>
       </c>
       <c r="C177" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F177" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G177" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -8066,13 +8169,47 @@
         <v>14</v>
       </c>
       <c r="C178" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="F178" t="s">
+        <v>101</v>
+      </c>
+      <c r="G178" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179">
+        <v>3</v>
+      </c>
+      <c r="B179" t="s">
+        <v>14</v>
+      </c>
+      <c r="C179" t="s">
+        <v>75</v>
+      </c>
+      <c r="F179" t="s">
+        <v>85</v>
+      </c>
+      <c r="G179" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180">
+        <v>3</v>
+      </c>
+      <c r="B180" t="s">
+        <v>14</v>
+      </c>
+      <c r="C180" t="s">
         <v>76</v>
       </c>
-      <c r="G178" t="s">
-        <v>92</v>
+      <c r="F180" t="s">
+        <v>102</v>
+      </c>
+      <c r="G180" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
